--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -4711,10 +4711,10 @@
         <v>32</v>
       </c>
       <c r="G27" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H27" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>40</v>
@@ -4752,10 +4752,10 @@
         <v>33</v>
       </c>
       <c r="G28" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H28" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>40</v>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="47">
   <si>
     <t>_ID</t>
   </si>
@@ -220,6 +220,21 @@
   </si>
   <si>
     <t>22,24,25,29,30</t>
+  </si>
+  <si>
+    <t>31,33</t>
+  </si>
+  <si>
+    <t>31,32,33,34,35,37,39,40</t>
+  </si>
+  <si>
+    <t>韧性倍率</t>
+  </si>
+  <si>
+    <t>32,34,35,39,40</t>
+  </si>
+  <si>
+    <t>增伤倍率</t>
   </si>
 </sst>
 </file>
@@ -1192,7 +1207,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:O70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="8.25" style="1" customWidth="1"/>
@@ -1206,7 +1221,7 @@
     <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:15">
+    <row r="3" ht="13.5" spans="3:15">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1247,7 +1262,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="3:15">
+    <row r="4" ht="13.5" spans="3:15">
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
@@ -1288,7 +1303,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="3:15">
+    <row r="5" ht="13.5" spans="3:15">
       <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
@@ -3733,8 +3748,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:O32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="C3:O45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="8.25" style="1" customWidth="1"/>
@@ -3748,7 +3763,7 @@
     <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" spans="3:15">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:15">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -3789,7 +3804,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="3:15">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:15">
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
@@ -3830,7 +3845,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="3:15">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:15">
       <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
@@ -4940,6 +4955,498 @@
         <v>1</v>
       </c>
       <c r="O32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:15">
+      <c r="C34" s="1">
+        <v>32</v>
+      </c>
+      <c r="D34" s="1">
+        <v>7</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="1">
+        <v>50</v>
+      </c>
+      <c r="H34" s="1">
+        <v>100</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1450</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1450</v>
+      </c>
+      <c r="L34" s="1">
+        <v>8</v>
+      </c>
+      <c r="M34" s="1">
+        <v>8</v>
+      </c>
+      <c r="N34" s="1">
+        <v>6</v>
+      </c>
+      <c r="O34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:15">
+      <c r="C35" s="1">
+        <v>33</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="1">
+        <v>10</v>
+      </c>
+      <c r="H35" s="1">
+        <v>20</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1450</v>
+      </c>
+      <c r="K35" s="1">
+        <v>1450</v>
+      </c>
+      <c r="L35" s="1">
+        <v>8</v>
+      </c>
+      <c r="M35" s="1">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
+        <v>3</v>
+      </c>
+      <c r="O35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="3:15">
+      <c r="C36" s="1">
+        <v>34</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2005</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" s="1">
+        <v>10</v>
+      </c>
+      <c r="H36" s="1">
+        <v>20</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1450</v>
+      </c>
+      <c r="K36" s="1">
+        <v>1450</v>
+      </c>
+      <c r="L36" s="1">
+        <v>8</v>
+      </c>
+      <c r="M36" s="1">
+        <v>8</v>
+      </c>
+      <c r="N36" s="3">
+        <v>3</v>
+      </c>
+      <c r="O36" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="3:15">
+      <c r="C37" s="1">
+        <v>35</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G37" s="1">
+        <v>10</v>
+      </c>
+      <c r="H37" s="1">
+        <v>20</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1450</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1450</v>
+      </c>
+      <c r="L37" s="1">
+        <v>8</v>
+      </c>
+      <c r="M37" s="1">
+        <v>8</v>
+      </c>
+      <c r="N37" s="3">
+        <v>3</v>
+      </c>
+      <c r="O37" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="3:15">
+      <c r="C38" s="1">
+        <v>36</v>
+      </c>
+      <c r="D38" s="1">
+        <v>33</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38" s="1">
+        <v>40</v>
+      </c>
+      <c r="H38" s="1">
+        <v>80</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1450</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1450</v>
+      </c>
+      <c r="L38" s="1">
+        <v>8</v>
+      </c>
+      <c r="M38" s="1">
+        <v>8</v>
+      </c>
+      <c r="N38" s="3">
+        <v>3</v>
+      </c>
+      <c r="O38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="3:15">
+      <c r="C39" s="1">
+        <v>37</v>
+      </c>
+      <c r="D39" s="1">
+        <v>34</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="1">
+        <v>40</v>
+      </c>
+      <c r="H39" s="1">
+        <v>80</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1450</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1450</v>
+      </c>
+      <c r="L39" s="1">
+        <v>8</v>
+      </c>
+      <c r="M39" s="1">
+        <v>8</v>
+      </c>
+      <c r="N39" s="3">
+        <v>3</v>
+      </c>
+      <c r="O39" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="3:15">
+      <c r="C40" s="1">
+        <v>38</v>
+      </c>
+      <c r="D40" s="1">
+        <v>35</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" s="1">
+        <v>40</v>
+      </c>
+      <c r="H40" s="1">
+        <v>80</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1450</v>
+      </c>
+      <c r="K40" s="1">
+        <v>1450</v>
+      </c>
+      <c r="L40" s="1">
+        <v>8</v>
+      </c>
+      <c r="M40" s="1">
+        <v>8</v>
+      </c>
+      <c r="N40" s="3">
+        <v>3</v>
+      </c>
+      <c r="O40" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="3:15">
+      <c r="C41" s="1">
+        <v>39</v>
+      </c>
+      <c r="D41" s="1">
+        <v>2001</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G41" s="1">
+        <v>10</v>
+      </c>
+      <c r="H41" s="1">
+        <v>20</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1450</v>
+      </c>
+      <c r="K41" s="1">
+        <v>1450</v>
+      </c>
+      <c r="L41" s="1">
+        <v>8</v>
+      </c>
+      <c r="M41" s="1">
+        <v>8</v>
+      </c>
+      <c r="N41" s="3">
+        <v>2</v>
+      </c>
+      <c r="O41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="3:15">
+      <c r="C42" s="1">
+        <v>40</v>
+      </c>
+      <c r="D42" s="1">
+        <v>2002</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G42" s="1">
+        <v>10</v>
+      </c>
+      <c r="H42" s="1">
+        <v>20</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1450</v>
+      </c>
+      <c r="K42" s="1">
+        <v>1450</v>
+      </c>
+      <c r="L42" s="1">
+        <v>8</v>
+      </c>
+      <c r="M42" s="1">
+        <v>8</v>
+      </c>
+      <c r="N42" s="3">
+        <v>3</v>
+      </c>
+      <c r="O42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="3:15">
+      <c r="C43" s="1">
+        <v>41</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2003</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" s="1">
+        <v>10</v>
+      </c>
+      <c r="H43" s="1">
+        <v>20</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1450</v>
+      </c>
+      <c r="K43" s="1">
+        <v>1450</v>
+      </c>
+      <c r="L43" s="1">
+        <v>8</v>
+      </c>
+      <c r="M43" s="1">
+        <v>8</v>
+      </c>
+      <c r="N43" s="3">
+        <v>3</v>
+      </c>
+      <c r="O43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="3:15">
+      <c r="C44" s="1">
+        <v>42</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2012</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="1">
+        <v>10</v>
+      </c>
+      <c r="H44" s="1">
+        <v>20</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1450</v>
+      </c>
+      <c r="K44" s="1">
+        <v>1450</v>
+      </c>
+      <c r="L44" s="1">
+        <v>8</v>
+      </c>
+      <c r="M44" s="1">
+        <v>8</v>
+      </c>
+      <c r="N44" s="3">
+        <v>2</v>
+      </c>
+      <c r="O44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="3:15">
+      <c r="C45" s="1">
+        <v>43</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G45" s="1">
+        <v>10</v>
+      </c>
+      <c r="H45" s="1">
+        <v>20</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1450</v>
+      </c>
+      <c r="K45" s="1">
+        <v>1450</v>
+      </c>
+      <c r="L45" s="1">
+        <v>8</v>
+      </c>
+      <c r="M45" s="1">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
+        <v>2</v>
+      </c>
+      <c r="O45" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="52">
   <si>
     <t>_ID</t>
   </si>
@@ -235,6 +235,21 @@
   </si>
   <si>
     <t>增伤倍率</t>
+  </si>
+  <si>
+    <t>41,43</t>
+  </si>
+  <si>
+    <t>幸运增幅</t>
+  </si>
+  <si>
+    <t>暴击增幅</t>
+  </si>
+  <si>
+    <t>41,42,43,44,45,47,49,50</t>
+  </si>
+  <si>
+    <t>42,44,45,49,50</t>
   </si>
 </sst>
 </file>
@@ -3748,7 +3763,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:O45"/>
+  <dimension ref="C3:O60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -3912,7 +3927,7 @@
         <v>750</v>
       </c>
       <c r="K6" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L6" s="1">
         <v>6</v>
@@ -3953,7 +3968,7 @@
         <v>750</v>
       </c>
       <c r="K7" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L7" s="1">
         <v>6</v>
@@ -3994,7 +4009,7 @@
         <v>750</v>
       </c>
       <c r="K8" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L8" s="1">
         <v>6</v>
@@ -4035,7 +4050,7 @@
         <v>750</v>
       </c>
       <c r="K9" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L9" s="1">
         <v>6</v>
@@ -4076,7 +4091,7 @@
         <v>750</v>
       </c>
       <c r="K10" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L10" s="1">
         <v>6</v>
@@ -4117,7 +4132,7 @@
         <v>750</v>
       </c>
       <c r="K11" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L11" s="1">
         <v>6</v>
@@ -4158,7 +4173,7 @@
         <v>750</v>
       </c>
       <c r="K12" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L12" s="1">
         <v>6</v>
@@ -4199,7 +4214,7 @@
         <v>750</v>
       </c>
       <c r="K13" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L13" s="1">
         <v>6</v>
@@ -4240,7 +4255,7 @@
         <v>750</v>
       </c>
       <c r="K14" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L14" s="1">
         <v>6</v>
@@ -4281,7 +4296,7 @@
         <v>750</v>
       </c>
       <c r="K15" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L15" s="1">
         <v>6</v>
@@ -4322,7 +4337,7 @@
         <v>750</v>
       </c>
       <c r="K16" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L16" s="1">
         <v>6</v>
@@ -4363,7 +4378,7 @@
         <v>750</v>
       </c>
       <c r="K17" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L17" s="1">
         <v>6</v>
@@ -4404,7 +4419,7 @@
         <v>750</v>
       </c>
       <c r="K18" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L18" s="1">
         <v>6</v>
@@ -4445,7 +4460,7 @@
         <v>750</v>
       </c>
       <c r="K19" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L19" s="1">
         <v>6</v>
@@ -4486,7 +4501,7 @@
         <v>750</v>
       </c>
       <c r="K20" s="1">
-        <v>1050</v>
+        <v>1800</v>
       </c>
       <c r="L20" s="1">
         <v>6</v>
@@ -5157,7 +5172,7 @@
         <v>8</v>
       </c>
       <c r="N38" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O38" s="1">
         <v>1</v>
@@ -5198,7 +5213,7 @@
         <v>8</v>
       </c>
       <c r="N39" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O39" s="1">
         <v>2</v>
@@ -5239,7 +5254,7 @@
         <v>8</v>
       </c>
       <c r="N40" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O40" s="1">
         <v>3</v>
@@ -5321,7 +5336,7 @@
         <v>8</v>
       </c>
       <c r="N42" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -5362,7 +5377,7 @@
         <v>8</v>
       </c>
       <c r="N43" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O43" s="1">
         <v>0</v>
@@ -5447,6 +5462,580 @@
         <v>2</v>
       </c>
       <c r="O45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:15">
+      <c r="C47" s="1">
+        <v>44</v>
+      </c>
+      <c r="D47" s="1">
+        <v>7</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="1">
+        <v>100</v>
+      </c>
+      <c r="H47" s="1">
+        <v>200</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K47" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L47" s="1">
+        <v>6</v>
+      </c>
+      <c r="M47" s="1">
+        <v>9</v>
+      </c>
+      <c r="N47" s="1">
+        <v>6</v>
+      </c>
+      <c r="O47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="3:15">
+      <c r="C48" s="1">
+        <v>45</v>
+      </c>
+      <c r="D48" s="1">
+        <v>55</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+      <c r="H48" s="1">
+        <v>2</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K48" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L48" s="1">
+        <v>6</v>
+      </c>
+      <c r="M48" s="1">
+        <v>9</v>
+      </c>
+      <c r="N48" s="1">
+        <v>1</v>
+      </c>
+      <c r="O48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15">
+      <c r="C49" s="1">
+        <v>46</v>
+      </c>
+      <c r="D49" s="1">
+        <v>54</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K49" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L49" s="1">
+        <v>6</v>
+      </c>
+      <c r="M49" s="1">
+        <v>9</v>
+      </c>
+      <c r="N49" s="1">
+        <v>1</v>
+      </c>
+      <c r="O49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15">
+      <c r="C50" s="1">
+        <v>47</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G50" s="1">
+        <v>15</v>
+      </c>
+      <c r="H50" s="1">
+        <v>30</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K50" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L50" s="1">
+        <v>6</v>
+      </c>
+      <c r="M50" s="1">
+        <v>9</v>
+      </c>
+      <c r="N50" s="3">
+        <v>3</v>
+      </c>
+      <c r="O50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15">
+      <c r="C51" s="1">
+        <v>48</v>
+      </c>
+      <c r="D51" s="1">
+        <v>2005</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G51" s="1">
+        <v>15</v>
+      </c>
+      <c r="H51" s="1">
+        <v>30</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K51" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L51" s="1">
+        <v>6</v>
+      </c>
+      <c r="M51" s="1">
+        <v>9</v>
+      </c>
+      <c r="N51" s="3">
+        <v>3</v>
+      </c>
+      <c r="O51" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15">
+      <c r="C52" s="1">
+        <v>49</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G52" s="1">
+        <v>15</v>
+      </c>
+      <c r="H52" s="1">
+        <v>30</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J52" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K52" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L52" s="1">
+        <v>6</v>
+      </c>
+      <c r="M52" s="1">
+        <v>9</v>
+      </c>
+      <c r="N52" s="3">
+        <v>3</v>
+      </c>
+      <c r="O52" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15">
+      <c r="C53" s="1">
+        <v>50</v>
+      </c>
+      <c r="D53" s="1">
+        <v>33</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G53" s="1">
+        <v>100</v>
+      </c>
+      <c r="H53" s="1">
+        <v>200</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K53" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L53" s="1">
+        <v>6</v>
+      </c>
+      <c r="M53" s="1">
+        <v>9</v>
+      </c>
+      <c r="N53" s="3">
+        <v>6</v>
+      </c>
+      <c r="O53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15">
+      <c r="C54" s="1">
+        <v>51</v>
+      </c>
+      <c r="D54" s="1">
+        <v>34</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G54" s="1">
+        <v>100</v>
+      </c>
+      <c r="H54" s="1">
+        <v>200</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K54" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L54" s="1">
+        <v>6</v>
+      </c>
+      <c r="M54" s="1">
+        <v>9</v>
+      </c>
+      <c r="N54" s="3">
+        <v>6</v>
+      </c>
+      <c r="O54" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15">
+      <c r="C55" s="1">
+        <v>52</v>
+      </c>
+      <c r="D55" s="1">
+        <v>35</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G55" s="1">
+        <v>100</v>
+      </c>
+      <c r="H55" s="1">
+        <v>200</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J55" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K55" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L55" s="1">
+        <v>6</v>
+      </c>
+      <c r="M55" s="1">
+        <v>9</v>
+      </c>
+      <c r="N55" s="3">
+        <v>6</v>
+      </c>
+      <c r="O55" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="3:15">
+      <c r="C56" s="1">
+        <v>53</v>
+      </c>
+      <c r="D56" s="1">
+        <v>2001</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G56" s="1">
+        <v>15</v>
+      </c>
+      <c r="H56" s="1">
+        <v>30</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J56" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K56" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L56" s="1">
+        <v>6</v>
+      </c>
+      <c r="M56" s="1">
+        <v>9</v>
+      </c>
+      <c r="N56" s="3">
+        <v>2</v>
+      </c>
+      <c r="O56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="3:15">
+      <c r="C57" s="1">
+        <v>54</v>
+      </c>
+      <c r="D57" s="1">
+        <v>2002</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G57" s="1">
+        <v>15</v>
+      </c>
+      <c r="H57" s="1">
+        <v>30</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J57" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K57" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L57" s="1">
+        <v>6</v>
+      </c>
+      <c r="M57" s="1">
+        <v>9</v>
+      </c>
+      <c r="N57" s="3">
+        <v>4</v>
+      </c>
+      <c r="O57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15">
+      <c r="C58" s="1">
+        <v>55</v>
+      </c>
+      <c r="D58" s="1">
+        <v>2003</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G58" s="1">
+        <v>15</v>
+      </c>
+      <c r="H58" s="1">
+        <v>30</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J58" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K58" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L58" s="1">
+        <v>6</v>
+      </c>
+      <c r="M58" s="1">
+        <v>9</v>
+      </c>
+      <c r="N58" s="3">
+        <v>4</v>
+      </c>
+      <c r="O58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15">
+      <c r="C59" s="1">
+        <v>56</v>
+      </c>
+      <c r="D59" s="1">
+        <v>2012</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G59" s="1">
+        <v>15</v>
+      </c>
+      <c r="H59" s="1">
+        <v>30</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K59" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L59" s="1">
+        <v>6</v>
+      </c>
+      <c r="M59" s="1">
+        <v>9</v>
+      </c>
+      <c r="N59" s="3">
+        <v>2</v>
+      </c>
+      <c r="O59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15">
+      <c r="C60" s="1">
+        <v>57</v>
+      </c>
+      <c r="D60" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G60" s="1">
+        <v>15</v>
+      </c>
+      <c r="H60" s="1">
+        <v>30</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1800</v>
+      </c>
+      <c r="K60" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L60" s="1">
+        <v>6</v>
+      </c>
+      <c r="M60" s="1">
+        <v>9</v>
+      </c>
+      <c r="N60" s="3">
+        <v>2</v>
+      </c>
+      <c r="O60" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="53">
   <si>
     <t>_ID</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>暴击增幅</t>
+  </si>
+  <si>
+    <t>49,50</t>
   </si>
   <si>
     <t>41,42,43,44,45,47,49,50</t>
@@ -5523,7 +5526,7 @@
         <v>1</v>
       </c>
       <c r="H48" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>47</v>
@@ -5564,10 +5567,10 @@
         <v>1</v>
       </c>
       <c r="H49" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J49" s="1">
         <v>1800</v>
@@ -5602,13 +5605,13 @@
         <v>28</v>
       </c>
       <c r="G50" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H50" s="1">
         <v>30</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J50" s="1">
         <v>1800</v>
@@ -5643,13 +5646,13 @@
         <v>29</v>
       </c>
       <c r="G51" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H51" s="1">
         <v>30</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J51" s="1">
         <v>1800</v>
@@ -5684,13 +5687,13 @@
         <v>30</v>
       </c>
       <c r="G52" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H52" s="1">
         <v>30</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J52" s="1">
         <v>1800</v>
@@ -5731,7 +5734,7 @@
         <v>200</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J53" s="1">
         <v>1800</v>
@@ -5772,7 +5775,7 @@
         <v>200</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J54" s="1">
         <v>1800</v>
@@ -5813,7 +5816,7 @@
         <v>200</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J55" s="1">
         <v>1800</v>
@@ -5848,13 +5851,13 @@
         <v>34</v>
       </c>
       <c r="G56" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H56" s="1">
         <v>30</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J56" s="1">
         <v>1800</v>
@@ -5889,13 +5892,13 @@
         <v>35</v>
       </c>
       <c r="G57" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H57" s="1">
         <v>30</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J57" s="1">
         <v>1800</v>
@@ -5930,13 +5933,13 @@
         <v>36</v>
       </c>
       <c r="G58" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H58" s="1">
         <v>30</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J58" s="1">
         <v>1800</v>
@@ -5971,13 +5974,13 @@
         <v>44</v>
       </c>
       <c r="G59" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H59" s="1">
         <v>30</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J59" s="1">
         <v>1800</v>
@@ -6012,13 +6015,13 @@
         <v>46</v>
       </c>
       <c r="G60" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H60" s="1">
         <v>30</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J60" s="1">
         <v>1800</v>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="50">
   <si>
     <t>_ID</t>
   </si>
@@ -117,16 +117,7 @@
     <t>PartList</t>
   </si>
   <si>
-    <t>StartLevel</t>
-  </si>
-  <si>
-    <t>EndLevel</t>
-  </si>
-  <si>
-    <t>StartQuality</t>
-  </si>
-  <si>
-    <t>EndQuality</t>
+    <t>Cycle</t>
   </si>
   <si>
     <t>MaxCount</t>
@@ -1224,7 +1215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:O70"/>
+  <dimension ref="C3:L70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1232,14 +1223,12 @@
     <col min="6" max="6" width="19.625" style="1" customWidth="1"/>
     <col min="7" max="8" width="13" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.625" style="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.625" style="1" customWidth="1"/>
-    <col min="13" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="19.25" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="10" max="12" width="13" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.25" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="13.5" spans="3:15">
+    <row r="3" ht="13.5" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1270,28 +1259,19 @@
       <c r="L3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="2" t="s">
+    </row>
+    <row r="4" ht="13.5" spans="3:12">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" ht="13.5" spans="3:15">
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>4</v>
@@ -1311,58 +1291,40 @@
       <c r="L4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="2" t="s">
+    </row>
+    <row r="5" ht="13.5" spans="3:12">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" ht="13.5" spans="3:15">
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="3:15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="3:12">
       <c r="C6" s="1">
         <v>701</v>
       </c>
@@ -1373,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1382,28 +1344,19 @@
         <v>2</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="L6" s="1">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1">
-        <v>5</v>
-      </c>
-      <c r="N6" s="1">
-        <v>6</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:12">
       <c r="C7" s="1">
         <v>702</v>
       </c>
@@ -1414,7 +1367,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -1423,28 +1376,19 @@
         <v>3</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J7" s="1">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>140</v>
+        <v>6</v>
       </c>
       <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1">
-        <v>5</v>
-      </c>
-      <c r="N7" s="1">
-        <v>6</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:12">
       <c r="C8" s="1">
         <v>703</v>
       </c>
@@ -1455,7 +1399,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1">
         <v>2</v>
@@ -1464,28 +1408,19 @@
         <v>4</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J8" s="1">
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1">
-        <v>210</v>
+        <v>6</v>
       </c>
       <c r="L8" s="1">
-        <v>1</v>
-      </c>
-      <c r="M8" s="1">
-        <v>5</v>
-      </c>
-      <c r="N8" s="1">
-        <v>6</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:12">
       <c r="C9" s="1">
         <v>704</v>
       </c>
@@ -1496,7 +1431,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G9" s="1">
         <v>2</v>
@@ -1505,28 +1440,19 @@
         <v>5</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J9" s="1">
-        <v>211</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>280</v>
+        <v>6</v>
       </c>
       <c r="L9" s="1">
-        <v>1</v>
-      </c>
-      <c r="M9" s="1">
-        <v>5</v>
-      </c>
-      <c r="N9" s="1">
-        <v>6</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:12">
       <c r="C10" s="1">
         <v>705</v>
       </c>
@@ -1537,7 +1463,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
@@ -1546,28 +1472,19 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J10" s="1">
-        <v>281</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="L10" s="1">
-        <v>1</v>
-      </c>
-      <c r="M10" s="1">
-        <v>5</v>
-      </c>
-      <c r="N10" s="1">
-        <v>6</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:12">
       <c r="C11" s="1">
         <v>801</v>
       </c>
@@ -1578,7 +1495,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1587,28 +1504,19 @@
         <v>5</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="L11" s="1">
-        <v>1</v>
-      </c>
-      <c r="M11" s="1">
-        <v>5</v>
-      </c>
-      <c r="N11" s="1">
-        <v>6</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:12">
       <c r="C12" s="1">
         <v>802</v>
       </c>
@@ -1619,7 +1527,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G12" s="1">
         <v>2</v>
@@ -1628,28 +1536,19 @@
         <v>10</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J12" s="1">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="L12" s="1">
-        <v>1</v>
-      </c>
-      <c r="M12" s="1">
-        <v>5</v>
-      </c>
-      <c r="N12" s="1">
-        <v>6</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:12">
       <c r="C13" s="1">
         <v>803</v>
       </c>
@@ -1660,7 +1559,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G13" s="1">
         <v>3</v>
@@ -1669,28 +1568,19 @@
         <v>15</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J13" s="1">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L13" s="1">
-        <v>1</v>
-      </c>
-      <c r="M13" s="1">
-        <v>5</v>
-      </c>
-      <c r="N13" s="1">
-        <v>6</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:12">
       <c r="C14" s="1">
         <v>804</v>
       </c>
@@ -1701,7 +1591,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1">
         <v>4</v>
@@ -1710,28 +1600,19 @@
         <v>20</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J14" s="1">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="L14" s="1">
-        <v>1</v>
-      </c>
-      <c r="M14" s="1">
-        <v>5</v>
-      </c>
-      <c r="N14" s="1">
-        <v>6</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:12">
       <c r="C15" s="1">
         <v>805</v>
       </c>
@@ -1742,7 +1623,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1">
         <v>5</v>
@@ -1751,28 +1632,19 @@
         <v>25</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J15" s="1">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="L15" s="1">
-        <v>1</v>
-      </c>
-      <c r="M15" s="1">
-        <v>5</v>
-      </c>
-      <c r="N15" s="1">
-        <v>6</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:12">
       <c r="C16" s="1">
         <v>806</v>
       </c>
@@ -1783,7 +1655,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16" s="1">
         <v>6</v>
@@ -1792,28 +1664,19 @@
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J16" s="1">
-        <v>251</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="L16" s="1">
-        <v>1</v>
-      </c>
-      <c r="M16" s="1">
-        <v>5</v>
-      </c>
-      <c r="N16" s="1">
-        <v>6</v>
-      </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:12">
       <c r="C17" s="1">
         <v>807</v>
       </c>
@@ -1824,7 +1687,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G17" s="1">
         <v>7</v>
@@ -1833,28 +1696,19 @@
         <v>35</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J17" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>350</v>
+        <v>6</v>
       </c>
       <c r="L17" s="1">
-        <v>1</v>
-      </c>
-      <c r="M17" s="1">
-        <v>5</v>
-      </c>
-      <c r="N17" s="1">
-        <v>6</v>
-      </c>
-      <c r="O17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12">
       <c r="C18" s="1">
         <v>808</v>
       </c>
@@ -1865,7 +1719,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" s="1">
         <v>8</v>
@@ -1874,28 +1728,19 @@
         <v>40</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J18" s="1">
-        <v>351</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>900</v>
+        <v>6</v>
       </c>
       <c r="L18" s="1">
-        <v>1</v>
-      </c>
-      <c r="M18" s="1">
-        <v>5</v>
-      </c>
-      <c r="N18" s="1">
-        <v>6</v>
-      </c>
-      <c r="O18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12">
       <c r="C19" s="1">
         <v>809</v>
       </c>
@@ -1906,7 +1751,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G19" s="1">
         <v>10</v>
@@ -1915,31 +1760,22 @@
         <v>50</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J19" s="1">
-        <v>901</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1">
-        <v>10000</v>
+        <v>6</v>
       </c>
       <c r="L19" s="1">
-        <v>1</v>
-      </c>
-      <c r="M19" s="1">
-        <v>5</v>
-      </c>
-      <c r="N19" s="1">
-        <v>6</v>
-      </c>
-      <c r="O19" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="9:9">
       <c r="I20" s="3"/>
     </row>
-    <row r="21" spans="3:15">
+    <row r="21" spans="3:12">
       <c r="C21" s="1">
         <v>1901</v>
       </c>
@@ -1950,7 +1786,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -1959,28 +1795,19 @@
         <v>5</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="L21" s="1">
-        <v>1</v>
-      </c>
-      <c r="M21" s="1">
-        <v>5</v>
-      </c>
-      <c r="N21" s="1">
-        <v>6</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12">
       <c r="C22" s="1">
         <v>1902</v>
       </c>
@@ -1991,7 +1818,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G22" s="1">
         <v>2</v>
@@ -2000,28 +1827,19 @@
         <v>10</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J22" s="1">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="L22" s="1">
-        <v>1</v>
-      </c>
-      <c r="M22" s="1">
-        <v>5</v>
-      </c>
-      <c r="N22" s="1">
-        <v>6</v>
-      </c>
-      <c r="O22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12">
       <c r="C23" s="1">
         <v>1903</v>
       </c>
@@ -2032,7 +1850,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G23" s="1">
         <v>3</v>
@@ -2041,28 +1859,19 @@
         <v>15</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J23" s="1">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L23" s="1">
-        <v>1</v>
-      </c>
-      <c r="M23" s="1">
-        <v>5</v>
-      </c>
-      <c r="N23" s="1">
-        <v>6</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12">
       <c r="C24" s="1">
         <v>1904</v>
       </c>
@@ -2073,7 +1882,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G24" s="1">
         <v>4</v>
@@ -2082,28 +1891,19 @@
         <v>20</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J24" s="1">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="K24" s="1">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="L24" s="1">
-        <v>1</v>
-      </c>
-      <c r="M24" s="1">
-        <v>5</v>
-      </c>
-      <c r="N24" s="1">
-        <v>6</v>
-      </c>
-      <c r="O24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12">
       <c r="C25" s="1">
         <v>1905</v>
       </c>
@@ -2114,7 +1914,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G25" s="1">
         <v>5</v>
@@ -2123,28 +1923,19 @@
         <v>25</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J25" s="1">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="K25" s="1">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="L25" s="1">
-        <v>1</v>
-      </c>
-      <c r="M25" s="1">
-        <v>5</v>
-      </c>
-      <c r="N25" s="1">
-        <v>6</v>
-      </c>
-      <c r="O25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12">
       <c r="C26" s="1">
         <v>1906</v>
       </c>
@@ -2155,7 +1946,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G26" s="1">
         <v>6</v>
@@ -2164,28 +1955,19 @@
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J26" s="1">
-        <v>251</v>
+        <v>1</v>
       </c>
       <c r="K26" s="1">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="L26" s="1">
-        <v>1</v>
-      </c>
-      <c r="M26" s="1">
-        <v>5</v>
-      </c>
-      <c r="N26" s="1">
-        <v>6</v>
-      </c>
-      <c r="O26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12">
       <c r="C27" s="1">
         <v>1907</v>
       </c>
@@ -2196,7 +1978,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
@@ -2205,28 +1987,19 @@
         <v>35</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J27" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1">
-        <v>350</v>
+        <v>6</v>
       </c>
       <c r="L27" s="1">
-        <v>1</v>
-      </c>
-      <c r="M27" s="1">
-        <v>5</v>
-      </c>
-      <c r="N27" s="1">
-        <v>6</v>
-      </c>
-      <c r="O27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12">
       <c r="C28" s="1">
         <v>1908</v>
       </c>
@@ -2237,7 +2010,7 @@
         <v>2</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G28" s="1">
         <v>8</v>
@@ -2246,28 +2019,19 @@
         <v>40</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J28" s="1">
-        <v>351</v>
+        <v>1</v>
       </c>
       <c r="K28" s="1">
-        <v>900</v>
+        <v>6</v>
       </c>
       <c r="L28" s="1">
-        <v>1</v>
-      </c>
-      <c r="M28" s="1">
-        <v>5</v>
-      </c>
-      <c r="N28" s="1">
-        <v>6</v>
-      </c>
-      <c r="O28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12">
       <c r="C29" s="1">
         <v>1909</v>
       </c>
@@ -2278,7 +2042,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
@@ -2287,31 +2051,22 @@
         <v>50</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J29" s="1">
-        <v>901</v>
+        <v>1</v>
       </c>
       <c r="K29" s="1">
-        <v>10000</v>
+        <v>6</v>
       </c>
       <c r="L29" s="1">
-        <v>1</v>
-      </c>
-      <c r="M29" s="1">
-        <v>5</v>
-      </c>
-      <c r="N29" s="1">
-        <v>6</v>
-      </c>
-      <c r="O29" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="9:9">
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="3:15">
+    <row r="31" spans="3:12">
       <c r="C31" s="1">
         <v>2001</v>
       </c>
@@ -2322,7 +2077,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -2331,28 +2086,19 @@
         <v>5</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="L31" s="1">
-        <v>1</v>
-      </c>
-      <c r="M31" s="1">
-        <v>5</v>
-      </c>
-      <c r="N31" s="1">
-        <v>6</v>
-      </c>
-      <c r="O31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12">
       <c r="C32" s="1">
         <v>2002</v>
       </c>
@@ -2363,7 +2109,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
@@ -2372,28 +2118,19 @@
         <v>10</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J32" s="1">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="L32" s="1">
-        <v>1</v>
-      </c>
-      <c r="M32" s="1">
-        <v>5</v>
-      </c>
-      <c r="N32" s="1">
-        <v>6</v>
-      </c>
-      <c r="O32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:12">
       <c r="C33" s="1">
         <v>2003</v>
       </c>
@@ -2404,7 +2141,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
@@ -2413,28 +2150,19 @@
         <v>15</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J33" s="1">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="K33" s="1">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L33" s="1">
-        <v>1</v>
-      </c>
-      <c r="M33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="1">
-        <v>6</v>
-      </c>
-      <c r="O33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:12">
       <c r="C34" s="1">
         <v>2004</v>
       </c>
@@ -2445,7 +2173,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
@@ -2454,28 +2182,19 @@
         <v>20</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J34" s="1">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="K34" s="1">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="L34" s="1">
-        <v>1</v>
-      </c>
-      <c r="M34" s="1">
-        <v>5</v>
-      </c>
-      <c r="N34" s="1">
-        <v>6</v>
-      </c>
-      <c r="O34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:12">
       <c r="C35" s="1">
         <v>2005</v>
       </c>
@@ -2486,7 +2205,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G35" s="1">
         <v>5</v>
@@ -2495,28 +2214,19 @@
         <v>25</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J35" s="1">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="K35" s="1">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="L35" s="1">
-        <v>1</v>
-      </c>
-      <c r="M35" s="1">
-        <v>5</v>
-      </c>
-      <c r="N35" s="1">
-        <v>6</v>
-      </c>
-      <c r="O35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:12">
       <c r="C36" s="1">
         <v>2006</v>
       </c>
@@ -2527,7 +2237,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G36" s="1">
         <v>6</v>
@@ -2536,28 +2246,19 @@
         <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J36" s="1">
-        <v>251</v>
+        <v>1</v>
       </c>
       <c r="K36" s="1">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="L36" s="1">
-        <v>1</v>
-      </c>
-      <c r="M36" s="1">
-        <v>5</v>
-      </c>
-      <c r="N36" s="1">
-        <v>6</v>
-      </c>
-      <c r="O36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:12">
       <c r="C37" s="1">
         <v>2007</v>
       </c>
@@ -2568,7 +2269,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G37" s="1">
         <v>7</v>
@@ -2577,28 +2278,19 @@
         <v>35</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J37" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="K37" s="1">
-        <v>350</v>
+        <v>6</v>
       </c>
       <c r="L37" s="1">
-        <v>1</v>
-      </c>
-      <c r="M37" s="1">
-        <v>5</v>
-      </c>
-      <c r="N37" s="1">
-        <v>6</v>
-      </c>
-      <c r="O37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="3:12">
       <c r="C38" s="1">
         <v>2008</v>
       </c>
@@ -2609,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G38" s="1">
         <v>8</v>
@@ -2618,28 +2310,19 @@
         <v>40</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J38" s="1">
-        <v>351</v>
+        <v>1</v>
       </c>
       <c r="K38" s="1">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="L38" s="1">
-        <v>1</v>
-      </c>
-      <c r="M38" s="1">
-        <v>5</v>
-      </c>
-      <c r="N38" s="1">
-        <v>6</v>
-      </c>
-      <c r="O38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="3:12">
       <c r="C39" s="1">
         <v>2401</v>
       </c>
@@ -2650,7 +2333,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
@@ -2659,28 +2342,19 @@
         <v>5</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" s="1">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="L39" s="1">
-        <v>1</v>
-      </c>
-      <c r="M39" s="1">
-        <v>5</v>
-      </c>
-      <c r="N39" s="1">
-        <v>6</v>
-      </c>
-      <c r="O39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="3:12">
       <c r="C40" s="1">
         <v>2402</v>
       </c>
@@ -2691,7 +2365,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -2700,28 +2374,19 @@
         <v>10</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J40" s="1">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="L40" s="1">
-        <v>1</v>
-      </c>
-      <c r="M40" s="1">
-        <v>5</v>
-      </c>
-      <c r="N40" s="1">
-        <v>6</v>
-      </c>
-      <c r="O40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="3:12">
       <c r="C41" s="1">
         <v>2403</v>
       </c>
@@ -2732,7 +2397,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
@@ -2741,28 +2406,19 @@
         <v>15</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J41" s="1">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="K41" s="1">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L41" s="1">
-        <v>1</v>
-      </c>
-      <c r="M41" s="1">
-        <v>5</v>
-      </c>
-      <c r="N41" s="1">
-        <v>6</v>
-      </c>
-      <c r="O41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="3:12">
       <c r="C42" s="1">
         <v>2404</v>
       </c>
@@ -2773,7 +2429,7 @@
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
@@ -2782,28 +2438,19 @@
         <v>20</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J42" s="1">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="K42" s="1">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="L42" s="1">
-        <v>1</v>
-      </c>
-      <c r="M42" s="1">
-        <v>5</v>
-      </c>
-      <c r="N42" s="1">
-        <v>6</v>
-      </c>
-      <c r="O42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="3:12">
       <c r="C43" s="1">
         <v>2405</v>
       </c>
@@ -2814,7 +2461,7 @@
         <v>2</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -2823,28 +2470,19 @@
         <v>25</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J43" s="1">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="K43" s="1">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="L43" s="1">
-        <v>1</v>
-      </c>
-      <c r="M43" s="1">
-        <v>5</v>
-      </c>
-      <c r="N43" s="1">
-        <v>6</v>
-      </c>
-      <c r="O43" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="3:12">
       <c r="C44" s="1">
         <v>2406</v>
       </c>
@@ -2855,7 +2493,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G44" s="1">
         <v>6</v>
@@ -2864,28 +2502,19 @@
         <v>30</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J44" s="1">
-        <v>251</v>
+        <v>1</v>
       </c>
       <c r="K44" s="1">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="L44" s="1">
-        <v>1</v>
-      </c>
-      <c r="M44" s="1">
-        <v>5</v>
-      </c>
-      <c r="N44" s="1">
-        <v>6</v>
-      </c>
-      <c r="O44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="3:12">
       <c r="C45" s="1">
         <v>2407</v>
       </c>
@@ -2896,7 +2525,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G45" s="1">
         <v>7</v>
@@ -2905,28 +2534,19 @@
         <v>35</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J45" s="1">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="K45" s="1">
-        <v>350</v>
+        <v>6</v>
       </c>
       <c r="L45" s="1">
-        <v>1</v>
-      </c>
-      <c r="M45" s="1">
-        <v>5</v>
-      </c>
-      <c r="N45" s="1">
-        <v>6</v>
-      </c>
-      <c r="O45" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="3:12">
       <c r="C46" s="1">
         <v>2408</v>
       </c>
@@ -2937,7 +2557,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G46" s="1">
         <v>8</v>
@@ -2946,28 +2566,19 @@
         <v>40</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J46" s="1">
-        <v>351</v>
+        <v>1</v>
       </c>
       <c r="K46" s="1">
-        <v>900</v>
+        <v>6</v>
       </c>
       <c r="L46" s="1">
-        <v>1</v>
-      </c>
-      <c r="M46" s="1">
-        <v>5</v>
-      </c>
-      <c r="N46" s="1">
-        <v>6</v>
-      </c>
-      <c r="O46" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:12">
       <c r="C47" s="1">
         <v>2409</v>
       </c>
@@ -2978,7 +2589,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G47" s="1">
         <v>10</v>
@@ -2987,28 +2598,19 @@
         <v>50</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J47" s="1">
-        <v>901</v>
+        <v>1</v>
       </c>
       <c r="K47" s="1">
-        <v>10000</v>
+        <v>6</v>
       </c>
       <c r="L47" s="1">
-        <v>1</v>
-      </c>
-      <c r="M47" s="1">
-        <v>5</v>
-      </c>
-      <c r="N47" s="1">
-        <v>6</v>
-      </c>
-      <c r="O47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12">
       <c r="C49" s="1">
         <v>2601</v>
       </c>
@@ -3019,7 +2621,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -3028,28 +2630,19 @@
         <v>3</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J49" s="1">
-        <v>0</v>
-      </c>
-      <c r="K49" s="1">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="K49" s="3">
+        <v>6</v>
       </c>
       <c r="L49" s="1">
-        <v>1</v>
-      </c>
-      <c r="M49" s="3">
-        <v>4</v>
-      </c>
-      <c r="N49" s="3">
-        <v>6</v>
-      </c>
-      <c r="O49" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12">
       <c r="C50" s="1">
         <v>2602</v>
       </c>
@@ -3060,7 +2653,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
@@ -3069,28 +2662,19 @@
         <v>4</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J50" s="1">
-        <v>101</v>
-      </c>
-      <c r="K50" s="1">
-        <v>200</v>
+        <v>1</v>
+      </c>
+      <c r="K50" s="3">
+        <v>6</v>
       </c>
       <c r="L50" s="1">
-        <v>1</v>
-      </c>
-      <c r="M50" s="3">
-        <v>4</v>
-      </c>
-      <c r="N50" s="3">
-        <v>6</v>
-      </c>
-      <c r="O50" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12">
       <c r="C51" s="1">
         <v>2603</v>
       </c>
@@ -3101,7 +2685,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G51" s="1">
         <v>1</v>
@@ -3110,28 +2694,19 @@
         <v>5</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J51" s="1">
-        <v>201</v>
-      </c>
-      <c r="K51" s="1">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="K51" s="3">
+        <v>6</v>
       </c>
       <c r="L51" s="1">
-        <v>1</v>
-      </c>
-      <c r="M51" s="3">
-        <v>4</v>
-      </c>
-      <c r="N51" s="3">
-        <v>6</v>
-      </c>
-      <c r="O51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12">
       <c r="C52" s="1">
         <v>2604</v>
       </c>
@@ -3142,7 +2717,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G52" s="1">
         <v>1</v>
@@ -3151,28 +2726,19 @@
         <v>5</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J52" s="1">
-        <v>301</v>
-      </c>
-      <c r="K52" s="1">
-        <v>400</v>
+        <v>1</v>
+      </c>
+      <c r="K52" s="3">
+        <v>6</v>
       </c>
       <c r="L52" s="1">
-        <v>1</v>
-      </c>
-      <c r="M52" s="3">
-        <v>4</v>
-      </c>
-      <c r="N52" s="3">
-        <v>6</v>
-      </c>
-      <c r="O52" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12">
       <c r="C53" s="1">
         <v>2605</v>
       </c>
@@ -3183,7 +2749,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G53" s="1">
         <v>1</v>
@@ -3192,28 +2758,19 @@
         <v>5</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J53" s="1">
-        <v>401</v>
-      </c>
-      <c r="K53" s="1">
-        <v>500</v>
+        <v>1</v>
+      </c>
+      <c r="K53" s="3">
+        <v>6</v>
       </c>
       <c r="L53" s="1">
-        <v>1</v>
-      </c>
-      <c r="M53" s="3">
-        <v>4</v>
-      </c>
-      <c r="N53" s="3">
-        <v>6</v>
-      </c>
-      <c r="O53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12">
       <c r="C54" s="1">
         <v>2606</v>
       </c>
@@ -3224,7 +2781,7 @@
         <v>2</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
@@ -3233,31 +2790,22 @@
         <v>5</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J54" s="1">
-        <v>501</v>
-      </c>
-      <c r="K54" s="1">
-        <v>1000</v>
+        <v>1</v>
+      </c>
+      <c r="K54" s="3">
+        <v>6</v>
       </c>
       <c r="L54" s="1">
-        <v>1</v>
-      </c>
-      <c r="M54" s="3">
-        <v>4</v>
-      </c>
-      <c r="N54" s="3">
-        <v>6</v>
-      </c>
-      <c r="O54" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="9:9">
       <c r="I55" s="3"/>
     </row>
-    <row r="56" spans="3:15">
+    <row r="56" spans="3:12">
       <c r="C56" s="1">
         <v>2701</v>
       </c>
@@ -3268,7 +2816,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -3277,28 +2825,19 @@
         <v>3</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J56" s="1">
-        <v>0</v>
-      </c>
-      <c r="K56" s="1">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="K56" s="3">
+        <v>6</v>
       </c>
       <c r="L56" s="1">
-        <v>1</v>
-      </c>
-      <c r="M56" s="3">
-        <v>4</v>
-      </c>
-      <c r="N56" s="3">
-        <v>6</v>
-      </c>
-      <c r="O56" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="3:12">
       <c r="C57" s="1">
         <v>2702</v>
       </c>
@@ -3309,7 +2848,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -3318,28 +2857,19 @@
         <v>4</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J57" s="1">
-        <v>101</v>
-      </c>
-      <c r="K57" s="1">
-        <v>200</v>
+        <v>1</v>
+      </c>
+      <c r="K57" s="3">
+        <v>6</v>
       </c>
       <c r="L57" s="1">
-        <v>1</v>
-      </c>
-      <c r="M57" s="3">
-        <v>4</v>
-      </c>
-      <c r="N57" s="3">
-        <v>6</v>
-      </c>
-      <c r="O57" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12">
       <c r="C58" s="1">
         <v>2703</v>
       </c>
@@ -3350,7 +2880,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G58" s="1">
         <v>1</v>
@@ -3359,28 +2889,19 @@
         <v>5</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J58" s="1">
-        <v>201</v>
-      </c>
-      <c r="K58" s="1">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="K58" s="3">
+        <v>6</v>
       </c>
       <c r="L58" s="1">
-        <v>1</v>
-      </c>
-      <c r="M58" s="3">
-        <v>4</v>
-      </c>
-      <c r="N58" s="3">
-        <v>6</v>
-      </c>
-      <c r="O58" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12">
       <c r="C59" s="1">
         <v>2704</v>
       </c>
@@ -3391,7 +2912,7 @@
         <v>2</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -3400,28 +2921,19 @@
         <v>5</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J59" s="1">
-        <v>301</v>
-      </c>
-      <c r="K59" s="1">
-        <v>400</v>
+        <v>1</v>
+      </c>
+      <c r="K59" s="3">
+        <v>6</v>
       </c>
       <c r="L59" s="1">
-        <v>1</v>
-      </c>
-      <c r="M59" s="3">
-        <v>4</v>
-      </c>
-      <c r="N59" s="3">
-        <v>6</v>
-      </c>
-      <c r="O59" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12">
       <c r="C60" s="1">
         <v>2705</v>
       </c>
@@ -3432,7 +2944,7 @@
         <v>2</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -3441,28 +2953,19 @@
         <v>5</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J60" s="1">
-        <v>401</v>
-      </c>
-      <c r="K60" s="1">
-        <v>500</v>
+        <v>1</v>
+      </c>
+      <c r="K60" s="3">
+        <v>6</v>
       </c>
       <c r="L60" s="1">
-        <v>1</v>
-      </c>
-      <c r="M60" s="3">
-        <v>4</v>
-      </c>
-      <c r="N60" s="3">
-        <v>6</v>
-      </c>
-      <c r="O60" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12">
       <c r="C61" s="1">
         <v>2706</v>
       </c>
@@ -3473,7 +2976,7 @@
         <v>2</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -3482,28 +2985,19 @@
         <v>5</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J61" s="1">
-        <v>501</v>
-      </c>
-      <c r="K61" s="1">
-        <v>1000</v>
+        <v>1</v>
+      </c>
+      <c r="K61" s="3">
+        <v>6</v>
       </c>
       <c r="L61" s="1">
-        <v>1</v>
-      </c>
-      <c r="M61" s="3">
-        <v>4</v>
-      </c>
-      <c r="N61" s="3">
-        <v>6</v>
-      </c>
-      <c r="O61" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12">
       <c r="C63" s="1">
         <v>2801</v>
       </c>
@@ -3514,7 +3008,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G63" s="1">
         <v>1</v>
@@ -3523,28 +3017,19 @@
         <v>3</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J63" s="1">
-        <v>0</v>
-      </c>
-      <c r="K63" s="1">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="K63" s="3">
+        <v>6</v>
       </c>
       <c r="L63" s="1">
-        <v>1</v>
-      </c>
-      <c r="M63" s="3">
-        <v>4</v>
-      </c>
-      <c r="N63" s="3">
-        <v>6</v>
-      </c>
-      <c r="O63" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12">
       <c r="C64" s="1">
         <v>2802</v>
       </c>
@@ -3555,7 +3040,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -3564,28 +3049,19 @@
         <v>4</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J64" s="1">
-        <v>101</v>
-      </c>
-      <c r="K64" s="1">
-        <v>200</v>
+        <v>1</v>
+      </c>
+      <c r="K64" s="3">
+        <v>6</v>
       </c>
       <c r="L64" s="1">
-        <v>1</v>
-      </c>
-      <c r="M64" s="3">
-        <v>4</v>
-      </c>
-      <c r="N64" s="3">
-        <v>6</v>
-      </c>
-      <c r="O64" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="3:12">
       <c r="C65" s="1">
         <v>2803</v>
       </c>
@@ -3596,7 +3072,7 @@
         <v>2</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -3605,28 +3081,19 @@
         <v>5</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J65" s="1">
-        <v>201</v>
-      </c>
-      <c r="K65" s="1">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="K65" s="3">
+        <v>6</v>
       </c>
       <c r="L65" s="1">
-        <v>1</v>
-      </c>
-      <c r="M65" s="3">
-        <v>4</v>
-      </c>
-      <c r="N65" s="3">
-        <v>6</v>
-      </c>
-      <c r="O65" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="3:12">
       <c r="C66" s="1">
         <v>2804</v>
       </c>
@@ -3637,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -3646,28 +3113,19 @@
         <v>5</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J66" s="1">
-        <v>301</v>
-      </c>
-      <c r="K66" s="1">
-        <v>400</v>
+        <v>1</v>
+      </c>
+      <c r="K66" s="3">
+        <v>6</v>
       </c>
       <c r="L66" s="1">
-        <v>1</v>
-      </c>
-      <c r="M66" s="3">
-        <v>4</v>
-      </c>
-      <c r="N66" s="3">
-        <v>6</v>
-      </c>
-      <c r="O66" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="3:12">
       <c r="C67" s="1">
         <v>2805</v>
       </c>
@@ -3678,7 +3136,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -3687,28 +3145,19 @@
         <v>5</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J67" s="1">
-        <v>401</v>
-      </c>
-      <c r="K67" s="1">
-        <v>500</v>
+        <v>1</v>
+      </c>
+      <c r="K67" s="3">
+        <v>6</v>
       </c>
       <c r="L67" s="1">
-        <v>1</v>
-      </c>
-      <c r="M67" s="3">
-        <v>4</v>
-      </c>
-      <c r="N67" s="3">
-        <v>6</v>
-      </c>
-      <c r="O67" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="3:12">
       <c r="C68" s="1">
         <v>2806</v>
       </c>
@@ -3719,7 +3168,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -3728,24 +3177,15 @@
         <v>5</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J68" s="1">
-        <v>501</v>
-      </c>
-      <c r="K68" s="1">
-        <v>1000</v>
+        <v>1</v>
+      </c>
+      <c r="K68" s="3">
+        <v>6</v>
       </c>
       <c r="L68" s="1">
-        <v>1</v>
-      </c>
-      <c r="M68" s="3">
-        <v>4</v>
-      </c>
-      <c r="N68" s="3">
-        <v>6</v>
-      </c>
-      <c r="O68" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3766,7 +3206,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:O60"/>
+  <dimension ref="C3:L60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -3774,14 +3214,13 @@
     <col min="6" max="6" width="19.625" style="1" customWidth="1"/>
     <col min="7" max="8" width="13" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.625" style="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.625" style="1" customWidth="1"/>
-    <col min="13" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="19.25" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.25" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:15">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -3812,28 +3251,19 @@
       <c r="L3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="2" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:12">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:15">
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>4</v>
@@ -3853,58 +3283,40 @@
       <c r="L4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="2" t="s">
+    </row>
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:12">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:15">
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="3:15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="3:12">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -3915,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -3924,28 +3336,19 @@
         <v>8</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J6" s="1">
-        <v>750</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>1800</v>
+        <v>6</v>
       </c>
       <c r="L6" s="1">
-        <v>6</v>
-      </c>
-      <c r="M6" s="1">
-        <v>6</v>
-      </c>
-      <c r="N6" s="1">
-        <v>6</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="3:12">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -3956,7 +3359,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -3965,28 +3368,19 @@
         <v>3</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J7" s="1">
-        <v>750</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1800</v>
+        <v>2</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>6</v>
-      </c>
-      <c r="M7" s="1">
-        <v>6</v>
-      </c>
-      <c r="N7" s="3">
-        <v>1</v>
-      </c>
-      <c r="O7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="3:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="3:12">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -3997,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -4006,28 +3400,19 @@
         <v>3</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J8" s="1">
-        <v>750</v>
-      </c>
-      <c r="K8" s="1">
-        <v>1800</v>
+        <v>2</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1</v>
       </c>
       <c r="L8" s="1">
-        <v>6</v>
-      </c>
-      <c r="M8" s="1">
-        <v>6</v>
-      </c>
-      <c r="N8" s="3">
-        <v>1</v>
-      </c>
-      <c r="O8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="3:15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="3:12">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -4038,7 +3423,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -4047,28 +3432,19 @@
         <v>3</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J9" s="1">
-        <v>750</v>
-      </c>
-      <c r="K9" s="1">
-        <v>1800</v>
+        <v>2</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>6</v>
-      </c>
-      <c r="M9" s="1">
-        <v>6</v>
-      </c>
-      <c r="N9" s="3">
-        <v>1</v>
-      </c>
-      <c r="O9" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="3:15">
+    <row r="10" s="1" customFormat="1" spans="3:12">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -4079,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -4088,28 +3464,19 @@
         <v>10</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J10" s="1">
-        <v>750</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1800</v>
+        <v>2</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2</v>
       </c>
       <c r="L10" s="1">
-        <v>6</v>
-      </c>
-      <c r="M10" s="1">
-        <v>6</v>
-      </c>
-      <c r="N10" s="3">
-        <v>2</v>
-      </c>
-      <c r="O10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="3:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="3:12">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -4120,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G11" s="1">
         <v>5</v>
@@ -4129,28 +3496,19 @@
         <v>10</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J11" s="1">
-        <v>750</v>
-      </c>
-      <c r="K11" s="1">
-        <v>1800</v>
+        <v>2</v>
+      </c>
+      <c r="K11" s="3">
+        <v>2</v>
       </c>
       <c r="L11" s="1">
-        <v>6</v>
-      </c>
-      <c r="M11" s="1">
-        <v>6</v>
-      </c>
-      <c r="N11" s="3">
-        <v>2</v>
-      </c>
-      <c r="O11" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="3:15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="3:12">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -4161,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1">
         <v>5</v>
@@ -4170,28 +3528,19 @@
         <v>10</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J12" s="1">
-        <v>750</v>
-      </c>
-      <c r="K12" s="1">
-        <v>1800</v>
+        <v>2</v>
+      </c>
+      <c r="K12" s="3">
+        <v>2</v>
       </c>
       <c r="L12" s="1">
-        <v>6</v>
-      </c>
-      <c r="M12" s="1">
-        <v>6</v>
-      </c>
-      <c r="N12" s="3">
-        <v>2</v>
-      </c>
-      <c r="O12" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="3:15">
+    <row r="13" s="1" customFormat="1" spans="3:12">
       <c r="C13" s="1">
         <v>9</v>
       </c>
@@ -4202,7 +3551,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
@@ -4211,28 +3560,19 @@
         <v>3</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J13" s="1">
-        <v>750</v>
-      </c>
-      <c r="K13" s="1">
-        <v>1800</v>
+        <v>2</v>
+      </c>
+      <c r="K13" s="3">
+        <v>1</v>
       </c>
       <c r="L13" s="1">
-        <v>6</v>
-      </c>
-      <c r="M13" s="1">
-        <v>6</v>
-      </c>
-      <c r="N13" s="3">
-        <v>1</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="3:12">
       <c r="C14" s="1">
         <v>10</v>
       </c>
@@ -4243,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -4252,28 +3592,19 @@
         <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J14" s="1">
-        <v>750</v>
-      </c>
-      <c r="K14" s="1">
-        <v>1800</v>
+        <v>2</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1</v>
       </c>
       <c r="L14" s="1">
-        <v>6</v>
-      </c>
-      <c r="M14" s="1">
-        <v>6</v>
-      </c>
-      <c r="N14" s="3">
-        <v>1</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="3:12">
       <c r="C15" s="1">
         <v>11</v>
       </c>
@@ -4284,7 +3615,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -4293,28 +3624,19 @@
         <v>3</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J15" s="1">
-        <v>750</v>
-      </c>
-      <c r="K15" s="1">
-        <v>1800</v>
+        <v>2</v>
+      </c>
+      <c r="K15" s="3">
+        <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>6</v>
-      </c>
-      <c r="M15" s="1">
-        <v>6</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="3:12">
       <c r="C16" s="1">
         <v>12</v>
       </c>
@@ -4325,7 +3647,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16" s="1">
         <v>25</v>
@@ -4334,28 +3656,19 @@
         <v>50</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J16" s="1">
-        <v>750</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1">
-        <v>1800</v>
+        <v>6</v>
       </c>
       <c r="L16" s="1">
-        <v>6</v>
-      </c>
-      <c r="M16" s="1">
-        <v>6</v>
-      </c>
-      <c r="N16" s="1">
-        <v>6</v>
-      </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="3:12">
       <c r="C17" s="1">
         <v>13</v>
       </c>
@@ -4366,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G17" s="1">
         <v>25</v>
@@ -4375,28 +3688,19 @@
         <v>50</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J17" s="1">
-        <v>750</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1">
-        <v>1800</v>
+        <v>6</v>
       </c>
       <c r="L17" s="1">
-        <v>6</v>
-      </c>
-      <c r="M17" s="1">
-        <v>6</v>
-      </c>
-      <c r="N17" s="1">
-        <v>6</v>
-      </c>
-      <c r="O17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="3:12">
       <c r="C18" s="1">
         <v>14</v>
       </c>
@@ -4407,7 +3711,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G18" s="1">
         <v>25</v>
@@ -4416,28 +3720,19 @@
         <v>50</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J18" s="1">
-        <v>750</v>
+        <v>2</v>
       </c>
       <c r="K18" s="1">
-        <v>1800</v>
+        <v>6</v>
       </c>
       <c r="L18" s="1">
-        <v>6</v>
-      </c>
-      <c r="M18" s="1">
-        <v>6</v>
-      </c>
-      <c r="N18" s="1">
-        <v>6</v>
-      </c>
-      <c r="O18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="3:12">
       <c r="C19" s="1">
         <v>15</v>
       </c>
@@ -4448,7 +3743,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G19" s="1">
         <v>25</v>
@@ -4457,28 +3752,19 @@
         <v>50</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J19" s="1">
-        <v>750</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1">
-        <v>1800</v>
+        <v>6</v>
       </c>
       <c r="L19" s="1">
-        <v>6</v>
-      </c>
-      <c r="M19" s="1">
-        <v>6</v>
-      </c>
-      <c r="N19" s="1">
-        <v>6</v>
-      </c>
-      <c r="O19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="3:12">
       <c r="C20" s="1">
         <v>16</v>
       </c>
@@ -4489,7 +3775,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -4498,34 +3784,24 @@
         <v>1</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J20" s="1">
-        <v>750</v>
-      </c>
-      <c r="K20" s="1">
-        <v>1800</v>
+        <v>2</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1</v>
       </c>
       <c r="L20" s="1">
-        <v>6</v>
-      </c>
-      <c r="M20" s="1">
-        <v>6</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1</v>
-      </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="9:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="9:12">
       <c r="I21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="3:15">
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="3:12">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -4536,7 +3812,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G22" s="1">
         <v>20</v>
@@ -4545,28 +3821,19 @@
         <v>50</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J22" s="1">
-        <v>1100</v>
+        <v>3</v>
       </c>
       <c r="K22" s="1">
-        <v>1100</v>
+        <v>6</v>
       </c>
       <c r="L22" s="1">
-        <v>7</v>
-      </c>
-      <c r="M22" s="1">
-        <v>7</v>
-      </c>
-      <c r="N22" s="1">
-        <v>6</v>
-      </c>
-      <c r="O22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="3:12">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -4577,7 +3844,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G23" s="1">
         <v>5</v>
@@ -4586,28 +3853,19 @@
         <v>10</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J23" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K23" s="1">
-        <v>1100</v>
+        <v>3</v>
+      </c>
+      <c r="K23" s="3">
+        <v>2</v>
       </c>
       <c r="L23" s="1">
-        <v>7</v>
-      </c>
-      <c r="M23" s="1">
-        <v>7</v>
-      </c>
-      <c r="N23" s="3">
-        <v>2</v>
-      </c>
-      <c r="O23" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="3:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="3:12">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -4618,7 +3876,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G24" s="1">
         <v>5</v>
@@ -4627,28 +3885,19 @@
         <v>10</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J24" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K24" s="1">
-        <v>1100</v>
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>2</v>
       </c>
       <c r="L24" s="1">
-        <v>7</v>
-      </c>
-      <c r="M24" s="1">
-        <v>7</v>
-      </c>
-      <c r="N24" s="3">
-        <v>2</v>
-      </c>
-      <c r="O24" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="3:15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="3:12">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -4659,7 +3908,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G25" s="1">
         <v>5</v>
@@ -4668,28 +3917,19 @@
         <v>10</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J25" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K25" s="1">
-        <v>1100</v>
+        <v>3</v>
+      </c>
+      <c r="K25" s="3">
+        <v>2</v>
       </c>
       <c r="L25" s="1">
-        <v>7</v>
-      </c>
-      <c r="M25" s="1">
-        <v>7</v>
-      </c>
-      <c r="N25" s="3">
-        <v>2</v>
-      </c>
-      <c r="O25" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="3:15">
+    <row r="26" s="1" customFormat="1" spans="3:12">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -4700,7 +3940,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G26" s="1">
         <v>20</v>
@@ -4709,28 +3949,19 @@
         <v>40</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J26" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K26" s="1">
-        <v>1100</v>
+        <v>3</v>
+      </c>
+      <c r="K26" s="3">
+        <v>3</v>
       </c>
       <c r="L26" s="1">
-        <v>7</v>
-      </c>
-      <c r="M26" s="1">
-        <v>7</v>
-      </c>
-      <c r="N26" s="3">
-        <v>3</v>
-      </c>
-      <c r="O26" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="3:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="3:12">
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -4741,7 +3972,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G27" s="1">
         <v>20</v>
@@ -4750,28 +3981,19 @@
         <v>40</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J27" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K27" s="1">
-        <v>1100</v>
+        <v>3</v>
+      </c>
+      <c r="K27" s="3">
+        <v>3</v>
       </c>
       <c r="L27" s="1">
-        <v>7</v>
-      </c>
-      <c r="M27" s="1">
-        <v>7</v>
-      </c>
-      <c r="N27" s="3">
-        <v>3</v>
-      </c>
-      <c r="O27" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="3:15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="3:12">
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -4782,7 +4004,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G28" s="1">
         <v>20</v>
@@ -4791,28 +4013,19 @@
         <v>40</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J28" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K28" s="1">
-        <v>1100</v>
+        <v>3</v>
+      </c>
+      <c r="K28" s="3">
+        <v>3</v>
       </c>
       <c r="L28" s="1">
-        <v>7</v>
-      </c>
-      <c r="M28" s="1">
-        <v>7</v>
-      </c>
-      <c r="N28" s="3">
         <v>3</v>
       </c>
-      <c r="O28" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="3:15">
+    </row>
+    <row r="29" s="1" customFormat="1" spans="3:12">
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -4823,7 +4036,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G29" s="1">
         <v>5</v>
@@ -4832,28 +4045,19 @@
         <v>10</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J29" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K29" s="1">
-        <v>1100</v>
+        <v>3</v>
+      </c>
+      <c r="K29" s="3">
+        <v>1</v>
       </c>
       <c r="L29" s="1">
-        <v>7</v>
-      </c>
-      <c r="M29" s="1">
-        <v>7</v>
-      </c>
-      <c r="N29" s="3">
-        <v>1</v>
-      </c>
-      <c r="O29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="3:12">
       <c r="C30" s="1">
         <v>25</v>
       </c>
@@ -4864,7 +4068,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G30" s="1">
         <v>5</v>
@@ -4873,28 +4077,19 @@
         <v>10</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J30" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K30" s="1">
-        <v>1100</v>
+        <v>3</v>
+      </c>
+      <c r="K30" s="3">
+        <v>3</v>
       </c>
       <c r="L30" s="1">
-        <v>7</v>
-      </c>
-      <c r="M30" s="1">
-        <v>7</v>
-      </c>
-      <c r="N30" s="3">
-        <v>3</v>
-      </c>
-      <c r="O30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="3:12">
       <c r="C31" s="1">
         <v>26</v>
       </c>
@@ -4905,7 +4100,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G31" s="1">
         <v>5</v>
@@ -4914,28 +4109,19 @@
         <v>10</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J31" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K31" s="1">
-        <v>1100</v>
+        <v>3</v>
+      </c>
+      <c r="K31" s="3">
+        <v>3</v>
       </c>
       <c r="L31" s="1">
-        <v>7</v>
-      </c>
-      <c r="M31" s="1">
-        <v>7</v>
-      </c>
-      <c r="N31" s="3">
-        <v>3</v>
-      </c>
-      <c r="O31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="3:12">
       <c r="C32" s="1">
         <v>31</v>
       </c>
@@ -4946,7 +4132,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G32" s="1">
         <v>5</v>
@@ -4955,28 +4141,19 @@
         <v>10</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J32" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K32" s="1">
-        <v>1100</v>
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
+        <v>1</v>
       </c>
       <c r="L32" s="1">
-        <v>7</v>
-      </c>
-      <c r="M32" s="1">
-        <v>7</v>
-      </c>
-      <c r="N32" s="3">
-        <v>1</v>
-      </c>
-      <c r="O32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:12">
       <c r="C34" s="1">
         <v>32</v>
       </c>
@@ -4987,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G34" s="1">
         <v>50</v>
@@ -4996,28 +4173,19 @@
         <v>100</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J34" s="1">
-        <v>1450</v>
+        <v>4</v>
       </c>
       <c r="K34" s="1">
-        <v>1450</v>
+        <v>6</v>
       </c>
       <c r="L34" s="1">
-        <v>8</v>
-      </c>
-      <c r="M34" s="1">
-        <v>8</v>
-      </c>
-      <c r="N34" s="1">
-        <v>6</v>
-      </c>
-      <c r="O34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:12">
       <c r="C35" s="1">
         <v>33</v>
       </c>
@@ -5028,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G35" s="1">
         <v>10</v>
@@ -5037,28 +4205,19 @@
         <v>20</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J35" s="1">
-        <v>1450</v>
-      </c>
-      <c r="K35" s="1">
-        <v>1450</v>
+        <v>4</v>
+      </c>
+      <c r="K35" s="3">
+        <v>3</v>
       </c>
       <c r="L35" s="1">
-        <v>8</v>
-      </c>
-      <c r="M35" s="1">
-        <v>8</v>
-      </c>
-      <c r="N35" s="3">
-        <v>3</v>
-      </c>
-      <c r="O35" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="3:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="3:12">
       <c r="C36" s="1">
         <v>34</v>
       </c>
@@ -5069,7 +4228,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
@@ -5078,28 +4237,19 @@
         <v>20</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J36" s="1">
-        <v>1450</v>
-      </c>
-      <c r="K36" s="1">
-        <v>1450</v>
+        <v>4</v>
+      </c>
+      <c r="K36" s="3">
+        <v>3</v>
       </c>
       <c r="L36" s="1">
-        <v>8</v>
-      </c>
-      <c r="M36" s="1">
-        <v>8</v>
-      </c>
-      <c r="N36" s="3">
-        <v>3</v>
-      </c>
-      <c r="O36" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="3:15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="3:12">
       <c r="C37" s="1">
         <v>35</v>
       </c>
@@ -5110,7 +4260,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G37" s="1">
         <v>10</v>
@@ -5119,28 +4269,19 @@
         <v>20</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J37" s="1">
-        <v>1450</v>
-      </c>
-      <c r="K37" s="1">
-        <v>1450</v>
+        <v>4</v>
+      </c>
+      <c r="K37" s="3">
+        <v>3</v>
       </c>
       <c r="L37" s="1">
-        <v>8</v>
-      </c>
-      <c r="M37" s="1">
-        <v>8</v>
-      </c>
-      <c r="N37" s="3">
         <v>3</v>
       </c>
-      <c r="O37" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="3:15">
+    </row>
+    <row r="38" spans="3:12">
       <c r="C38" s="1">
         <v>36</v>
       </c>
@@ -5151,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G38" s="1">
         <v>40</v>
@@ -5160,28 +4301,19 @@
         <v>80</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J38" s="1">
-        <v>1450</v>
-      </c>
-      <c r="K38" s="1">
-        <v>1450</v>
+        <v>4</v>
+      </c>
+      <c r="K38" s="3">
+        <v>4</v>
       </c>
       <c r="L38" s="1">
-        <v>8</v>
-      </c>
-      <c r="M38" s="1">
-        <v>8</v>
-      </c>
-      <c r="N38" s="3">
-        <v>4</v>
-      </c>
-      <c r="O38" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="3:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="3:12">
       <c r="C39" s="1">
         <v>37</v>
       </c>
@@ -5192,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G39" s="1">
         <v>40</v>
@@ -5201,28 +4333,19 @@
         <v>80</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J39" s="1">
-        <v>1450</v>
-      </c>
-      <c r="K39" s="1">
-        <v>1450</v>
+        <v>4</v>
+      </c>
+      <c r="K39" s="3">
+        <v>4</v>
       </c>
       <c r="L39" s="1">
-        <v>8</v>
-      </c>
-      <c r="M39" s="1">
-        <v>8</v>
-      </c>
-      <c r="N39" s="3">
-        <v>4</v>
-      </c>
-      <c r="O39" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="3:15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="3:12">
       <c r="C40" s="1">
         <v>38</v>
       </c>
@@ -5233,7 +4356,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G40" s="1">
         <v>40</v>
@@ -5242,28 +4365,19 @@
         <v>80</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J40" s="1">
-        <v>1450</v>
-      </c>
-      <c r="K40" s="1">
-        <v>1450</v>
+        <v>4</v>
+      </c>
+      <c r="K40" s="3">
+        <v>4</v>
       </c>
       <c r="L40" s="1">
-        <v>8</v>
-      </c>
-      <c r="M40" s="1">
-        <v>8</v>
-      </c>
-      <c r="N40" s="3">
-        <v>4</v>
-      </c>
-      <c r="O40" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="3:15">
+    <row r="41" spans="3:12">
       <c r="C41" s="1">
         <v>39</v>
       </c>
@@ -5274,7 +4388,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G41" s="1">
         <v>10</v>
@@ -5283,28 +4397,19 @@
         <v>20</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J41" s="1">
-        <v>1450</v>
-      </c>
-      <c r="K41" s="1">
-        <v>1450</v>
+        <v>4</v>
+      </c>
+      <c r="K41" s="3">
+        <v>2</v>
       </c>
       <c r="L41" s="1">
-        <v>8</v>
-      </c>
-      <c r="M41" s="1">
-        <v>8</v>
-      </c>
-      <c r="N41" s="3">
-        <v>2</v>
-      </c>
-      <c r="O41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="3:12">
       <c r="C42" s="1">
         <v>40</v>
       </c>
@@ -5315,7 +4420,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G42" s="1">
         <v>10</v>
@@ -5324,28 +4429,19 @@
         <v>20</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J42" s="1">
-        <v>1450</v>
-      </c>
-      <c r="K42" s="1">
-        <v>1450</v>
+        <v>4</v>
+      </c>
+      <c r="K42" s="3">
+        <v>4</v>
       </c>
       <c r="L42" s="1">
-        <v>8</v>
-      </c>
-      <c r="M42" s="1">
-        <v>8</v>
-      </c>
-      <c r="N42" s="3">
-        <v>4</v>
-      </c>
-      <c r="O42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="3:12">
       <c r="C43" s="1">
         <v>41</v>
       </c>
@@ -5356,7 +4452,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G43" s="1">
         <v>10</v>
@@ -5365,28 +4461,19 @@
         <v>20</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J43" s="1">
-        <v>1450</v>
-      </c>
-      <c r="K43" s="1">
-        <v>1450</v>
+        <v>4</v>
+      </c>
+      <c r="K43" s="3">
+        <v>4</v>
       </c>
       <c r="L43" s="1">
-        <v>8</v>
-      </c>
-      <c r="M43" s="1">
-        <v>8</v>
-      </c>
-      <c r="N43" s="3">
-        <v>4</v>
-      </c>
-      <c r="O43" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="3:12">
       <c r="C44" s="1">
         <v>42</v>
       </c>
@@ -5397,7 +4484,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G44" s="1">
         <v>10</v>
@@ -5406,28 +4493,19 @@
         <v>20</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J44" s="1">
-        <v>1450</v>
-      </c>
-      <c r="K44" s="1">
-        <v>1450</v>
+        <v>4</v>
+      </c>
+      <c r="K44" s="3">
+        <v>2</v>
       </c>
       <c r="L44" s="1">
-        <v>8</v>
-      </c>
-      <c r="M44" s="1">
-        <v>8</v>
-      </c>
-      <c r="N44" s="3">
-        <v>2</v>
-      </c>
-      <c r="O44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="3:12">
       <c r="C45" s="1">
         <v>43</v>
       </c>
@@ -5438,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G45" s="1">
         <v>10</v>
@@ -5447,28 +4525,19 @@
         <v>20</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J45" s="1">
-        <v>1450</v>
-      </c>
-      <c r="K45" s="1">
-        <v>1450</v>
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
+        <v>2</v>
       </c>
       <c r="L45" s="1">
-        <v>8</v>
-      </c>
-      <c r="M45" s="1">
-        <v>8</v>
-      </c>
-      <c r="N45" s="3">
-        <v>2</v>
-      </c>
-      <c r="O45" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:12">
       <c r="C47" s="1">
         <v>44</v>
       </c>
@@ -5479,7 +4548,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G47" s="1">
         <v>100</v>
@@ -5488,28 +4557,19 @@
         <v>200</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J47" s="1">
-        <v>1800</v>
+        <v>5</v>
       </c>
       <c r="K47" s="1">
-        <v>1800</v>
+        <v>6</v>
       </c>
       <c r="L47" s="1">
-        <v>6</v>
-      </c>
-      <c r="M47" s="1">
-        <v>9</v>
-      </c>
-      <c r="N47" s="1">
-        <v>6</v>
-      </c>
-      <c r="O47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="3:12">
       <c r="C48" s="1">
         <v>45</v>
       </c>
@@ -5520,7 +4580,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -5529,28 +4589,19 @@
         <v>1</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J48" s="1">
-        <v>1800</v>
+        <v>5</v>
       </c>
       <c r="K48" s="1">
-        <v>1800</v>
+        <v>1</v>
       </c>
       <c r="L48" s="1">
-        <v>6</v>
-      </c>
-      <c r="M48" s="1">
-        <v>9</v>
-      </c>
-      <c r="N48" s="1">
-        <v>1</v>
-      </c>
-      <c r="O48" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12">
       <c r="C49" s="1">
         <v>46</v>
       </c>
@@ -5561,7 +4612,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G49" s="1">
         <v>1</v>
@@ -5570,28 +4621,19 @@
         <v>1</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J49" s="1">
-        <v>1800</v>
+        <v>5</v>
       </c>
       <c r="K49" s="1">
-        <v>1800</v>
+        <v>1</v>
       </c>
       <c r="L49" s="1">
-        <v>6</v>
-      </c>
-      <c r="M49" s="1">
-        <v>9</v>
-      </c>
-      <c r="N49" s="1">
-        <v>1</v>
-      </c>
-      <c r="O49" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12">
       <c r="C50" s="1">
         <v>47</v>
       </c>
@@ -5602,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G50" s="1">
         <v>10</v>
@@ -5611,28 +4653,19 @@
         <v>30</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J50" s="1">
-        <v>1800</v>
-      </c>
-      <c r="K50" s="1">
-        <v>1800</v>
+        <v>5</v>
+      </c>
+      <c r="K50" s="3">
+        <v>3</v>
       </c>
       <c r="L50" s="1">
-        <v>6</v>
-      </c>
-      <c r="M50" s="1">
-        <v>9</v>
-      </c>
-      <c r="N50" s="3">
-        <v>3</v>
-      </c>
-      <c r="O50" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="3:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12">
       <c r="C51" s="1">
         <v>48</v>
       </c>
@@ -5643,7 +4676,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G51" s="1">
         <v>10</v>
@@ -5652,28 +4685,19 @@
         <v>30</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J51" s="1">
-        <v>1800</v>
-      </c>
-      <c r="K51" s="1">
-        <v>1800</v>
+        <v>5</v>
+      </c>
+      <c r="K51" s="3">
+        <v>3</v>
       </c>
       <c r="L51" s="1">
-        <v>6</v>
-      </c>
-      <c r="M51" s="1">
-        <v>9</v>
-      </c>
-      <c r="N51" s="3">
-        <v>3</v>
-      </c>
-      <c r="O51" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="3:15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12">
       <c r="C52" s="1">
         <v>49</v>
       </c>
@@ -5684,7 +4708,7 @@
         <v>1</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G52" s="1">
         <v>10</v>
@@ -5693,28 +4717,19 @@
         <v>30</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J52" s="1">
-        <v>1800</v>
-      </c>
-      <c r="K52" s="1">
-        <v>1800</v>
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
+        <v>3</v>
       </c>
       <c r="L52" s="1">
-        <v>6</v>
-      </c>
-      <c r="M52" s="1">
-        <v>9</v>
-      </c>
-      <c r="N52" s="3">
         <v>3</v>
       </c>
-      <c r="O52" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:15">
+    </row>
+    <row r="53" spans="3:12">
       <c r="C53" s="1">
         <v>50</v>
       </c>
@@ -5725,7 +4740,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G53" s="1">
         <v>100</v>
@@ -5734,28 +4749,19 @@
         <v>200</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J53" s="1">
-        <v>1800</v>
-      </c>
-      <c r="K53" s="1">
-        <v>1800</v>
+        <v>5</v>
+      </c>
+      <c r="K53" s="3">
+        <v>6</v>
       </c>
       <c r="L53" s="1">
-        <v>6</v>
-      </c>
-      <c r="M53" s="1">
-        <v>9</v>
-      </c>
-      <c r="N53" s="3">
-        <v>6</v>
-      </c>
-      <c r="O53" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="3:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12">
       <c r="C54" s="1">
         <v>51</v>
       </c>
@@ -5766,7 +4772,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G54" s="1">
         <v>100</v>
@@ -5775,28 +4781,19 @@
         <v>200</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J54" s="1">
-        <v>1800</v>
-      </c>
-      <c r="K54" s="1">
-        <v>1800</v>
+        <v>5</v>
+      </c>
+      <c r="K54" s="3">
+        <v>6</v>
       </c>
       <c r="L54" s="1">
-        <v>6</v>
-      </c>
-      <c r="M54" s="1">
-        <v>9</v>
-      </c>
-      <c r="N54" s="3">
-        <v>6</v>
-      </c>
-      <c r="O54" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="3:15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12">
       <c r="C55" s="1">
         <v>52</v>
       </c>
@@ -5807,7 +4804,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G55" s="1">
         <v>100</v>
@@ -5816,28 +4813,19 @@
         <v>200</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J55" s="1">
-        <v>1800</v>
-      </c>
-      <c r="K55" s="1">
-        <v>1800</v>
+        <v>5</v>
+      </c>
+      <c r="K55" s="3">
+        <v>6</v>
       </c>
       <c r="L55" s="1">
-        <v>6</v>
-      </c>
-      <c r="M55" s="1">
-        <v>9</v>
-      </c>
-      <c r="N55" s="3">
-        <v>6</v>
-      </c>
-      <c r="O55" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="3:15">
+    <row r="56" spans="3:12">
       <c r="C56" s="1">
         <v>53</v>
       </c>
@@ -5848,7 +4836,7 @@
         <v>1</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G56" s="1">
         <v>10</v>
@@ -5857,28 +4845,19 @@
         <v>30</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J56" s="1">
-        <v>1800</v>
-      </c>
-      <c r="K56" s="1">
-        <v>1800</v>
+        <v>5</v>
+      </c>
+      <c r="K56" s="3">
+        <v>2</v>
       </c>
       <c r="L56" s="1">
-        <v>6</v>
-      </c>
-      <c r="M56" s="1">
-        <v>9</v>
-      </c>
-      <c r="N56" s="3">
-        <v>2</v>
-      </c>
-      <c r="O56" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="3:12">
       <c r="C57" s="1">
         <v>54</v>
       </c>
@@ -5889,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G57" s="1">
         <v>10</v>
@@ -5898,28 +4877,19 @@
         <v>30</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J57" s="1">
-        <v>1800</v>
-      </c>
-      <c r="K57" s="1">
-        <v>1800</v>
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
+        <v>4</v>
       </c>
       <c r="L57" s="1">
-        <v>6</v>
-      </c>
-      <c r="M57" s="1">
-        <v>9</v>
-      </c>
-      <c r="N57" s="3">
-        <v>4</v>
-      </c>
-      <c r="O57" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12">
       <c r="C58" s="1">
         <v>55</v>
       </c>
@@ -5930,7 +4900,7 @@
         <v>1</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G58" s="1">
         <v>10</v>
@@ -5939,28 +4909,19 @@
         <v>30</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J58" s="1">
-        <v>1800</v>
-      </c>
-      <c r="K58" s="1">
-        <v>1800</v>
+        <v>5</v>
+      </c>
+      <c r="K58" s="3">
+        <v>4</v>
       </c>
       <c r="L58" s="1">
-        <v>6</v>
-      </c>
-      <c r="M58" s="1">
-        <v>9</v>
-      </c>
-      <c r="N58" s="3">
-        <v>4</v>
-      </c>
-      <c r="O58" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12">
       <c r="C59" s="1">
         <v>56</v>
       </c>
@@ -5971,7 +4932,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G59" s="1">
         <v>10</v>
@@ -5980,28 +4941,19 @@
         <v>30</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J59" s="1">
-        <v>1800</v>
-      </c>
-      <c r="K59" s="1">
-        <v>1800</v>
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
+        <v>2</v>
       </c>
       <c r="L59" s="1">
-        <v>6</v>
-      </c>
-      <c r="M59" s="1">
-        <v>9</v>
-      </c>
-      <c r="N59" s="3">
-        <v>2</v>
-      </c>
-      <c r="O59" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12">
       <c r="C60" s="1">
         <v>57</v>
       </c>
@@ -6012,7 +4964,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G60" s="1">
         <v>10</v>
@@ -6021,24 +4973,15 @@
         <v>30</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J60" s="1">
-        <v>1800</v>
-      </c>
-      <c r="K60" s="1">
-        <v>1800</v>
+        <v>5</v>
+      </c>
+      <c r="K60" s="3">
+        <v>2</v>
       </c>
       <c r="L60" s="1">
-        <v>6</v>
-      </c>
-      <c r="M60" s="1">
-        <v>9</v>
-      </c>
-      <c r="N60" s="3">
-        <v>2</v>
-      </c>
-      <c r="O60" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
     <sheet name="红装" sheetId="2" r:id="rId2"/>
+    <sheet name="生肖" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -93,8 +94,41 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+ID* 10 + level
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="61">
   <si>
     <t>_ID</t>
   </si>
@@ -244,6 +278,39 @@
   </si>
   <si>
     <t>42,44,45,49,50</t>
+  </si>
+  <si>
+    <t>神话攻击</t>
+  </si>
+  <si>
+    <t>1,4,7,10</t>
+  </si>
+  <si>
+    <t>神话防御</t>
+  </si>
+  <si>
+    <t>2,5,8,11</t>
+  </si>
+  <si>
+    <t>神话生命</t>
+  </si>
+  <si>
+    <t>3,6,9,12</t>
+  </si>
+  <si>
+    <t>物理倍率</t>
+  </si>
+  <si>
+    <t>物伤倍率</t>
+  </si>
+  <si>
+    <t>法伤倍率</t>
+  </si>
+  <si>
+    <t>道伤倍率</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
   </si>
 </sst>
 </file>
@@ -4995,4 +5062,457 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C3:L17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="8.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.25" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:12">
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:12">
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:12">
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="3:12">
+      <c r="C6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>91</v>
+      </c>
+      <c r="E6" s="1">
+        <v>6</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>10</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="1">
+        <v>99</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="3:12">
+      <c r="C7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>92</v>
+      </c>
+      <c r="E7" s="1">
+        <v>6</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>10</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="1">
+        <v>99</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="3:12">
+      <c r="C8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>93</v>
+      </c>
+      <c r="E8" s="1">
+        <v>6</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>10</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="1">
+        <v>99</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="3:12">
+      <c r="C9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E9" s="1">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1">
+        <v>50</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="1">
+        <v>99</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="3:12">
+      <c r="C10" s="1">
+        <v>1005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2005</v>
+      </c>
+      <c r="E10" s="1">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="1">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1">
+        <v>50</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="1">
+        <v>99</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="3:12">
+      <c r="C11" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E11" s="1">
+        <v>7</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="1">
+        <v>25</v>
+      </c>
+      <c r="H11" s="1">
+        <v>50</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="1">
+        <v>99</v>
+      </c>
+      <c r="K11" s="3">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="3:12">
+      <c r="C12" s="1">
+        <v>1007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2007</v>
+      </c>
+      <c r="E12" s="1">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="1">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1">
+        <v>50</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" s="1">
+        <v>99</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="3:12">
+      <c r="C13" s="1">
+        <v>1008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2008</v>
+      </c>
+      <c r="E13" s="1">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="1">
+        <v>25</v>
+      </c>
+      <c r="H13" s="1">
+        <v>50</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="1">
+        <v>99</v>
+      </c>
+      <c r="K13" s="3">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="3:12">
+      <c r="C14" s="1">
+        <v>1009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2009</v>
+      </c>
+      <c r="E14" s="1">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="1">
+        <v>25</v>
+      </c>
+      <c r="H14" s="1">
+        <v>50</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="1">
+        <v>99</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="3:12">
+      <c r="C15" s="1">
+        <v>1010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E15" s="1">
+        <v>9</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="1">
+        <v>25</v>
+      </c>
+      <c r="H15" s="1">
+        <v>50</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J15" s="1">
+        <v>99</v>
+      </c>
+      <c r="K15" s="3">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="11:11">
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="9:11">
+      <c r="I17" s="3"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -489,12 +489,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5290,7 +5290,7 @@
         <v>25</v>
       </c>
       <c r="H9" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>51</v>
@@ -5322,7 +5322,7 @@
         <v>25</v>
       </c>
       <c r="H10" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>53</v>
@@ -5354,7 +5354,7 @@
         <v>25</v>
       </c>
       <c r="H11" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>55</v>
@@ -5386,7 +5386,7 @@
         <v>25</v>
       </c>
       <c r="H12" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>51</v>
@@ -5418,7 +5418,7 @@
         <v>25</v>
       </c>
       <c r="H13" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>53</v>
@@ -5450,7 +5450,7 @@
         <v>25</v>
       </c>
       <c r="H14" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>55</v>
@@ -5482,7 +5482,7 @@
         <v>25</v>
       </c>
       <c r="H15" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>60</v>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="62">
   <si>
     <t>_ID</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>42,44,45,49,50</t>
+  </si>
+  <si>
+    <t>破韧倍率</t>
   </si>
   <si>
     <t>神话攻击</t>
@@ -1839,7 +1842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="9:9">
+    <row r="20" spans="3:12">
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="3:12">
@@ -2130,7 +2133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="9:9">
+    <row r="30" spans="3:12">
       <c r="I30" s="3"/>
     </row>
     <row r="31" spans="3:12">
@@ -2869,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="9:9">
+    <row r="55" spans="3:12">
       <c r="I55" s="3"/>
     </row>
     <row r="56" spans="3:12">
@@ -3273,7 +3276,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L60"/>
+  <dimension ref="C3:L76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -3863,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="9:12">
+    <row r="21" s="1" customFormat="1" spans="3:12">
       <c r="I21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
@@ -5049,6 +5052,486 @@
         <v>2</v>
       </c>
       <c r="L60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12">
+      <c r="C62" s="1">
+        <v>58</v>
+      </c>
+      <c r="D62" s="1">
+        <v>7</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" s="1">
+        <v>200</v>
+      </c>
+      <c r="H62" s="1">
+        <v>400</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J62" s="1">
+        <v>6</v>
+      </c>
+      <c r="K62" s="1">
+        <v>6</v>
+      </c>
+      <c r="L62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12">
+      <c r="C63" s="1">
+        <v>59</v>
+      </c>
+      <c r="D63" s="1">
+        <v>55</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G63" s="1">
+        <v>2</v>
+      </c>
+      <c r="H63" s="1">
+        <v>2</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J63" s="1">
+        <v>6</v>
+      </c>
+      <c r="K63" s="1">
+        <v>1</v>
+      </c>
+      <c r="L63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12">
+      <c r="C64" s="1">
+        <v>60</v>
+      </c>
+      <c r="D64" s="1">
+        <v>54</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G64" s="1">
+        <v>2</v>
+      </c>
+      <c r="H64" s="1">
+        <v>2</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J64" s="1">
+        <v>6</v>
+      </c>
+      <c r="K64" s="1">
+        <v>1</v>
+      </c>
+      <c r="L64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="3:12">
+      <c r="C65" s="1">
+        <v>61</v>
+      </c>
+      <c r="D65" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G65" s="1">
+        <v>15</v>
+      </c>
+      <c r="H65" s="1">
+        <v>40</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J65" s="1">
+        <v>6</v>
+      </c>
+      <c r="K65" s="3">
+        <v>3</v>
+      </c>
+      <c r="L65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="3:12">
+      <c r="C66" s="1">
+        <v>62</v>
+      </c>
+      <c r="D66" s="1">
+        <v>2005</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="1">
+        <v>15</v>
+      </c>
+      <c r="H66" s="1">
+        <v>40</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J66" s="1">
+        <v>6</v>
+      </c>
+      <c r="K66" s="3">
+        <v>3</v>
+      </c>
+      <c r="L66" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="3:12">
+      <c r="C67" s="1">
+        <v>63</v>
+      </c>
+      <c r="D67" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E67" s="1">
+        <v>1</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G67" s="1">
+        <v>15</v>
+      </c>
+      <c r="H67" s="1">
+        <v>40</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J67" s="1">
+        <v>6</v>
+      </c>
+      <c r="K67" s="3">
+        <v>3</v>
+      </c>
+      <c r="L67" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="3:12">
+      <c r="C68" s="1">
+        <v>64</v>
+      </c>
+      <c r="D68" s="1">
+        <v>33</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G68" s="1">
+        <v>200</v>
+      </c>
+      <c r="H68" s="1">
+        <v>400</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J68" s="1">
+        <v>6</v>
+      </c>
+      <c r="K68" s="3">
+        <v>6</v>
+      </c>
+      <c r="L68" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="3:12">
+      <c r="C69" s="1">
+        <v>65</v>
+      </c>
+      <c r="D69" s="1">
+        <v>34</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G69" s="1">
+        <v>200</v>
+      </c>
+      <c r="H69" s="1">
+        <v>400</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J69" s="1">
+        <v>6</v>
+      </c>
+      <c r="K69" s="3">
+        <v>6</v>
+      </c>
+      <c r="L69" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="3:12">
+      <c r="C70" s="1">
+        <v>66</v>
+      </c>
+      <c r="D70" s="1">
+        <v>35</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G70" s="1">
+        <v>200</v>
+      </c>
+      <c r="H70" s="1">
+        <v>400</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J70" s="1">
+        <v>6</v>
+      </c>
+      <c r="K70" s="3">
+        <v>6</v>
+      </c>
+      <c r="L70" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="3:12">
+      <c r="C71" s="1">
+        <v>67</v>
+      </c>
+      <c r="D71" s="1">
+        <v>2001</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G71" s="1">
+        <v>15</v>
+      </c>
+      <c r="H71" s="1">
+        <v>40</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J71" s="1">
+        <v>6</v>
+      </c>
+      <c r="K71" s="3">
+        <v>2</v>
+      </c>
+      <c r="L71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="3:12">
+      <c r="C72" s="1">
+        <v>68</v>
+      </c>
+      <c r="D72" s="1">
+        <v>2002</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G72" s="1">
+        <v>15</v>
+      </c>
+      <c r="H72" s="1">
+        <v>40</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J72" s="1">
+        <v>6</v>
+      </c>
+      <c r="K72" s="3">
+        <v>4</v>
+      </c>
+      <c r="L72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="3:12">
+      <c r="C73" s="1">
+        <v>69</v>
+      </c>
+      <c r="D73" s="1">
+        <v>2003</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G73" s="1">
+        <v>15</v>
+      </c>
+      <c r="H73" s="1">
+        <v>40</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J73" s="1">
+        <v>6</v>
+      </c>
+      <c r="K73" s="3">
+        <v>4</v>
+      </c>
+      <c r="L73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="3:12">
+      <c r="C74" s="1">
+        <v>70</v>
+      </c>
+      <c r="D74" s="1">
+        <v>2012</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G74" s="1">
+        <v>15</v>
+      </c>
+      <c r="H74" s="1">
+        <v>40</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J74" s="1">
+        <v>6</v>
+      </c>
+      <c r="K74" s="3">
+        <v>2</v>
+      </c>
+      <c r="L74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="3:12">
+      <c r="C75" s="1">
+        <v>71</v>
+      </c>
+      <c r="D75" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G75" s="1">
+        <v>15</v>
+      </c>
+      <c r="H75" s="1">
+        <v>40</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J75" s="1">
+        <v>6</v>
+      </c>
+      <c r="K75" s="3">
+        <v>2</v>
+      </c>
+      <c r="L75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="3:12">
+      <c r="C76" s="1">
+        <v>72</v>
+      </c>
+      <c r="D76" s="1">
+        <v>2013</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G76" s="1">
+        <v>15</v>
+      </c>
+      <c r="H76" s="1">
+        <v>40</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J76" s="1">
+        <v>6</v>
+      </c>
+      <c r="K76" s="3">
+        <v>2</v>
+      </c>
+      <c r="L76" s="1">
         <v>0</v>
       </c>
     </row>
@@ -5188,7 +5671,7 @@
         <v>6</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -5197,7 +5680,7 @@
         <v>10</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J6" s="1">
         <v>99</v>
@@ -5220,7 +5703,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -5229,7 +5712,7 @@
         <v>10</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J7" s="1">
         <v>99</v>
@@ -5252,7 +5735,7 @@
         <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -5261,7 +5744,7 @@
         <v>10</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J8" s="1">
         <v>99</v>
@@ -5293,7 +5776,7 @@
         <v>100</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J9" s="1">
         <v>99</v>
@@ -5325,7 +5808,7 @@
         <v>100</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J10" s="1">
         <v>99</v>
@@ -5348,7 +5831,7 @@
         <v>7</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="1">
         <v>25</v>
@@ -5357,7 +5840,7 @@
         <v>100</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J11" s="1">
         <v>99</v>
@@ -5380,7 +5863,7 @@
         <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G12" s="1">
         <v>25</v>
@@ -5389,7 +5872,7 @@
         <v>100</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J12" s="1">
         <v>99</v>
@@ -5412,7 +5895,7 @@
         <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G13" s="1">
         <v>25</v>
@@ -5421,7 +5904,7 @@
         <v>100</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J13" s="1">
         <v>99</v>
@@ -5444,7 +5927,7 @@
         <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G14" s="1">
         <v>25</v>
@@ -5453,7 +5936,7 @@
         <v>100</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J14" s="1">
         <v>99</v>
@@ -5485,7 +5968,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J15" s="1">
         <v>99</v>
@@ -5497,7 +5980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="11:11">
+    <row r="16" s="1" customFormat="1" spans="3:12">
       <c r="K16" s="3"/>
     </row>
     <row r="17" s="1" customFormat="1" spans="9:11">

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="66">
   <si>
     <t>_ID</t>
   </si>
@@ -278,6 +278,18 @@
   </si>
   <si>
     <t>42,44,45,49,50</t>
+  </si>
+  <si>
+    <t>51,53</t>
+  </si>
+  <si>
+    <t>59,50</t>
+  </si>
+  <si>
+    <t>51,52,53,54,55,57,59,50</t>
+  </si>
+  <si>
+    <t>52,54,55,59,50</t>
   </si>
   <si>
     <t>破韧倍率</t>
@@ -492,12 +504,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5075,7 +5087,7 @@
         <v>400</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J62" s="1">
         <v>6</v>
@@ -5107,7 +5119,7 @@
         <v>2</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J63" s="1">
         <v>6</v>
@@ -5139,7 +5151,7 @@
         <v>2</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J64" s="1">
         <v>6</v>
@@ -5171,7 +5183,7 @@
         <v>40</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J65" s="1">
         <v>6</v>
@@ -5203,7 +5215,7 @@
         <v>40</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J66" s="1">
         <v>6</v>
@@ -5235,7 +5247,7 @@
         <v>40</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J67" s="1">
         <v>6</v>
@@ -5267,7 +5279,7 @@
         <v>400</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J68" s="1">
         <v>6</v>
@@ -5299,7 +5311,7 @@
         <v>400</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J69" s="1">
         <v>6</v>
@@ -5331,7 +5343,7 @@
         <v>400</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J70" s="1">
         <v>6</v>
@@ -5363,7 +5375,7 @@
         <v>40</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J71" s="1">
         <v>6</v>
@@ -5395,7 +5407,7 @@
         <v>40</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J72" s="1">
         <v>6</v>
@@ -5427,7 +5439,7 @@
         <v>40</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J73" s="1">
         <v>6</v>
@@ -5459,7 +5471,7 @@
         <v>40</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J74" s="1">
         <v>6</v>
@@ -5491,7 +5503,7 @@
         <v>40</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J75" s="1">
         <v>6</v>
@@ -5514,7 +5526,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G76" s="1">
         <v>15</v>
@@ -5523,7 +5535,7 @@
         <v>40</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J76" s="1">
         <v>6</v>
@@ -5671,7 +5683,7 @@
         <v>6</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -5680,7 +5692,7 @@
         <v>10</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J6" s="1">
         <v>99</v>
@@ -5703,7 +5715,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -5712,7 +5724,7 @@
         <v>10</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J7" s="1">
         <v>99</v>
@@ -5735,7 +5747,7 @@
         <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -5744,7 +5756,7 @@
         <v>10</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J8" s="1">
         <v>99</v>
@@ -5776,7 +5788,7 @@
         <v>100</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J9" s="1">
         <v>99</v>
@@ -5808,7 +5820,7 @@
         <v>100</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J10" s="1">
         <v>99</v>
@@ -5831,7 +5843,7 @@
         <v>7</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G11" s="1">
         <v>25</v>
@@ -5840,7 +5852,7 @@
         <v>100</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J11" s="1">
         <v>99</v>
@@ -5863,7 +5875,7 @@
         <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G12" s="1">
         <v>25</v>
@@ -5872,7 +5884,7 @@
         <v>100</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J12" s="1">
         <v>99</v>
@@ -5895,7 +5907,7 @@
         <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G13" s="1">
         <v>25</v>
@@ -5904,7 +5916,7 @@
         <v>100</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J13" s="1">
         <v>99</v>
@@ -5927,7 +5939,7 @@
         <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G14" s="1">
         <v>25</v>
@@ -5936,7 +5948,7 @@
         <v>100</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J14" s="1">
         <v>99</v>
@@ -5968,7 +5980,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J15" s="1">
         <v>99</v>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -5125,7 +5125,7 @@
         <v>6</v>
       </c>
       <c r="K63" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L63" s="1">
         <v>0</v>
@@ -5157,7 +5157,7 @@
         <v>6</v>
       </c>
       <c r="K64" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="1">
         <v>0</v>
@@ -5413,7 +5413,7 @@
         <v>6</v>
       </c>
       <c r="K72" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L72" s="1">
         <v>0</v>
@@ -5445,7 +5445,7 @@
         <v>6</v>
       </c>
       <c r="K73" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L73" s="1">
         <v>0</v>
@@ -5477,7 +5477,7 @@
         <v>6</v>
       </c>
       <c r="K74" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L74" s="1">
         <v>0</v>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -283,13 +283,13 @@
     <t>51,53</t>
   </si>
   <si>
-    <t>59,50</t>
-  </si>
-  <si>
-    <t>51,52,53,54,55,57,59,50</t>
-  </si>
-  <si>
-    <t>52,54,55,59,50</t>
+    <t>59,60</t>
+  </si>
+  <si>
+    <t>51,52,53,54,55,57,59,60</t>
+  </si>
+  <si>
+    <t>52,54,55,59,60</t>
   </si>
   <si>
     <t>破韧倍率</t>
@@ -504,12 +504,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="70">
   <si>
     <t>_ID</t>
   </si>
@@ -326,6 +326,18 @@
   </si>
   <si>
     <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+  </si>
+  <si>
+    <t>13,17,19,22</t>
+  </si>
+  <si>
+    <t>14,18,20,23</t>
+  </si>
+  <si>
+    <t>15,19,21,24</t>
+  </si>
+  <si>
+    <t>13,14,15,16,17,18,19,20,21,22,23,24</t>
   </si>
 </sst>
 </file>
@@ -504,12 +516,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5562,14 +5574,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L17"/>
+  <dimension ref="C3:L26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="8.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="19.625" style="1" customWidth="1"/>
     <col min="7" max="8" width="13" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.5833333333333" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
     <col min="11" max="12" width="13" style="1" customWidth="1"/>
     <col min="13" max="13" width="19.25" style="1" customWidth="1"/>
@@ -5995,10 +6007,325 @@
     <row r="16" s="1" customFormat="1" spans="3:12">
       <c r="K16" s="3"/>
     </row>
-    <row r="17" s="1" customFormat="1" spans="9:11">
-      <c r="I17" s="3"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="3"/>
+    <row r="17" s="1" customFormat="1" spans="3:12">
+      <c r="C17" s="1">
+        <v>1011</v>
+      </c>
+      <c r="D17" s="1">
+        <v>91</v>
+      </c>
+      <c r="E17" s="1">
+        <v>6</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>12</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J17" s="1">
+        <v>99</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12">
+      <c r="C18" s="1">
+        <v>1012</v>
+      </c>
+      <c r="D18" s="1">
+        <v>92</v>
+      </c>
+      <c r="E18" s="1">
+        <v>6</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>12</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J18" s="1">
+        <v>99</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12">
+      <c r="C19" s="1">
+        <v>1013</v>
+      </c>
+      <c r="D19" s="1">
+        <v>93</v>
+      </c>
+      <c r="E19" s="1">
+        <v>6</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>12</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J19" s="1">
+        <v>99</v>
+      </c>
+      <c r="K19" s="3">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:12">
+      <c r="C20" s="1">
+        <v>1014</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E20" s="1">
+        <v>7</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="1">
+        <v>25</v>
+      </c>
+      <c r="H20" s="1">
+        <v>200</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" s="1">
+        <v>99</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12">
+      <c r="C21" s="1">
+        <v>1015</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2005</v>
+      </c>
+      <c r="E21" s="1">
+        <v>7</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="1">
+        <v>25</v>
+      </c>
+      <c r="H21" s="1">
+        <v>200</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J21" s="1">
+        <v>99</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12">
+      <c r="C22" s="1">
+        <v>1016</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E22" s="1">
+        <v>7</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" s="1">
+        <v>25</v>
+      </c>
+      <c r="H22" s="1">
+        <v>200</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J22" s="1">
+        <v>99</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12">
+      <c r="C23" s="1">
+        <v>1017</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2007</v>
+      </c>
+      <c r="E23" s="1">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="1">
+        <v>25</v>
+      </c>
+      <c r="H23" s="1">
+        <v>200</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J23" s="1">
+        <v>99</v>
+      </c>
+      <c r="K23" s="3">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12">
+      <c r="C24" s="1">
+        <v>1018</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2008</v>
+      </c>
+      <c r="E24" s="1">
+        <v>8</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" s="1">
+        <v>25</v>
+      </c>
+      <c r="H24" s="1">
+        <v>200</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J24" s="1">
+        <v>99</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12">
+      <c r="C25" s="1">
+        <v>1019</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2009</v>
+      </c>
+      <c r="E25" s="1">
+        <v>8</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="1">
+        <v>25</v>
+      </c>
+      <c r="H25" s="1">
+        <v>200</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J25" s="1">
+        <v>99</v>
+      </c>
+      <c r="K25" s="3">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12">
+      <c r="C26" s="1">
+        <v>1020</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E26" s="1">
+        <v>9</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="1">
+        <v>25</v>
+      </c>
+      <c r="H26" s="1">
+        <v>200</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J26" s="1">
+        <v>99</v>
+      </c>
+      <c r="K26" s="3">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -328,13 +328,13 @@
     <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
   </si>
   <si>
-    <t>13,17,19,22</t>
-  </si>
-  <si>
-    <t>14,18,20,23</t>
-  </si>
-  <si>
-    <t>15,19,21,24</t>
+    <t>13,16,19,22</t>
+  </si>
+  <si>
+    <t>14,17,20,23</t>
+  </si>
+  <si>
+    <t>15,18,21,24</t>
   </si>
   <si>
     <t>13,14,15,16,17,18,19,20,21,22,23,24</t>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -6024,7 +6024,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>66</v>
@@ -6056,7 +6056,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>67</v>
@@ -6088,7 +6088,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>68</v>

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="74">
   <si>
     <t>_ID</t>
   </si>
@@ -338,6 +338,18 @@
   </si>
   <si>
     <t>13,14,15,16,17,18,19,20,21,22,23,24</t>
+  </si>
+  <si>
+    <t>25,28,31,34</t>
+  </si>
+  <si>
+    <t>26,29,32,35</t>
+  </si>
+  <si>
+    <t>27,30,33,36</t>
+  </si>
+  <si>
+    <t>25,26,27,28,29,30,31,32,33,34,35,36</t>
   </si>
 </sst>
 </file>
@@ -5574,7 +5586,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L26"/>
+  <dimension ref="C3:L38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -6327,6 +6339,326 @@
         <v>0</v>
       </c>
     </row>
+    <row r="29" spans="3:12">
+      <c r="C29" s="1">
+        <v>1021</v>
+      </c>
+      <c r="D29" s="1">
+        <v>91</v>
+      </c>
+      <c r="E29" s="1">
+        <v>6</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
+        <v>18</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J29" s="1">
+        <v>99</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12">
+      <c r="C30" s="1">
+        <v>1022</v>
+      </c>
+      <c r="D30" s="1">
+        <v>92</v>
+      </c>
+      <c r="E30" s="1">
+        <v>6</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
+        <v>18</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="J30" s="1">
+        <v>99</v>
+      </c>
+      <c r="K30" s="3">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12">
+      <c r="C31" s="1">
+        <v>1023</v>
+      </c>
+      <c r="D31" s="1">
+        <v>93</v>
+      </c>
+      <c r="E31" s="1">
+        <v>6</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" s="1">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1">
+        <v>18</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J31" s="1">
+        <v>99</v>
+      </c>
+      <c r="K31" s="3">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12">
+      <c r="C32" s="1">
+        <v>1024</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E32" s="1">
+        <v>7</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" s="1">
+        <v>25</v>
+      </c>
+      <c r="H32" s="1">
+        <v>300</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J32" s="1">
+        <v>99</v>
+      </c>
+      <c r="K32" s="3">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:12">
+      <c r="C33" s="1">
+        <v>1025</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2005</v>
+      </c>
+      <c r="E33" s="1">
+        <v>7</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="1">
+        <v>25</v>
+      </c>
+      <c r="H33" s="1">
+        <v>300</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33" s="1">
+        <v>99</v>
+      </c>
+      <c r="K33" s="3">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:12">
+      <c r="C34" s="1">
+        <v>1026</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E34" s="1">
+        <v>7</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" s="1">
+        <v>25</v>
+      </c>
+      <c r="H34" s="1">
+        <v>300</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J34" s="1">
+        <v>99</v>
+      </c>
+      <c r="K34" s="3">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:12">
+      <c r="C35" s="1">
+        <v>1027</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2007</v>
+      </c>
+      <c r="E35" s="1">
+        <v>8</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G35" s="1">
+        <v>25</v>
+      </c>
+      <c r="H35" s="1">
+        <v>300</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J35" s="1">
+        <v>99</v>
+      </c>
+      <c r="K35" s="3">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:12">
+      <c r="C36" s="1">
+        <v>1028</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2008</v>
+      </c>
+      <c r="E36" s="1">
+        <v>8</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G36" s="1">
+        <v>25</v>
+      </c>
+      <c r="H36" s="1">
+        <v>300</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="J36" s="1">
+        <v>99</v>
+      </c>
+      <c r="K36" s="3">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:12">
+      <c r="C37" s="1">
+        <v>1029</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2009</v>
+      </c>
+      <c r="E37" s="1">
+        <v>8</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G37" s="1">
+        <v>25</v>
+      </c>
+      <c r="H37" s="1">
+        <v>300</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J37" s="1">
+        <v>99</v>
+      </c>
+      <c r="K37" s="3">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="3:12">
+      <c r="C38" s="1">
+        <v>1030</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E38" s="1">
+        <v>9</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G38" s="1">
+        <v>25</v>
+      </c>
+      <c r="H38" s="1">
+        <v>300</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J38" s="1">
+        <v>99</v>
+      </c>
+      <c r="K38" s="3">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">

--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -6452,7 +6452,7 @@
         <v>25</v>
       </c>
       <c r="H32" s="1">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>70</v>
@@ -6484,7 +6484,7 @@
         <v>25</v>
       </c>
       <c r="H33" s="1">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>71</v>
@@ -6516,7 +6516,7 @@
         <v>25</v>
       </c>
       <c r="H34" s="1">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>72</v>
@@ -6548,7 +6548,7 @@
         <v>25</v>
       </c>
       <c r="H35" s="1">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>70</v>
@@ -6580,7 +6580,7 @@
         <v>25</v>
       </c>
       <c r="H36" s="1">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>71</v>
@@ -6612,7 +6612,7 @@
         <v>25</v>
       </c>
       <c r="H37" s="1">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>72</v>
@@ -6644,7 +6644,7 @@
         <v>25</v>
       </c>
       <c r="H38" s="1">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>73</v>
